--- a/data/Arisdorf/investment_decision/Arisdorf_MFH_2005-2014_investment_decision.xlsx
+++ b/data/Arisdorf/investment_decision/Arisdorf_MFH_2005-2014_investment_decision.xlsx
@@ -17,8 +17,8 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
-    <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="165" formatCode="yyyy-mm-dd h:mm:ss"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -58,12 +58,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -440,61 +441,61 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>scen_all_invested_available_unit</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>scale_MW</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>scen_all_candidate_unit</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>scen_base_invested_available_unit</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>scale_MW</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>scen_base_candidate_unit</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>scen_cp_dr_invested_available_unit</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>scen_cp_dr_candidate_unit</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>scen_cp_cu_invested_available_unit</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>scen_cp_cu_candidate_unit</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>scen_all_invested_available_unit</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>scen_all_candidate_unit</t>
-        </is>
-      </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="n">
+      <c r="A2" s="3" t="n">
         <v>46023</v>
       </c>
       <c r="B2" t="n">
-        <v>6.012635090781166</v>
+        <v>5.182471626152436</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -505,33 +506,33 @@
         <v>0.003</v>
       </c>
       <c r="E2" t="n">
-        <v>1499.657904743305</v>
+        <v>1500.192929592385</v>
       </c>
       <c r="F2" t="n">
-        <v>6.027760775346405</v>
+        <v>5.221614923124662</v>
       </c>
       <c r="G2" t="n">
-        <v>1499.657904743305</v>
+        <v>1500.192929592385</v>
       </c>
       <c r="H2" t="n">
-        <v>6.027760775346406</v>
+        <v>5.182471626152437</v>
       </c>
       <c r="I2" t="n">
-        <v>1499.657904743305</v>
+        <v>1500.192929592385</v>
       </c>
       <c r="J2" t="n">
-        <v>6.141230981562329</v>
+        <v>5.228096530781166</v>
       </c>
       <c r="K2" t="n">
-        <v>1499.657904743305</v>
+        <v>1500.192929592385</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="n">
+      <c r="A3" s="3" t="n">
         <v>47849</v>
       </c>
       <c r="B3" t="n">
-        <v>8.089573475596609</v>
+        <v>8.570364869034156</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -542,33 +543,33 @@
         <v>0.003</v>
       </c>
       <c r="E3" t="n">
-        <v>1499.657904743305</v>
+        <v>1500.192929592385</v>
       </c>
       <c r="F3" t="n">
-        <v>8.089573475596609</v>
+        <v>7.578689065828083</v>
       </c>
       <c r="G3" t="n">
-        <v>1499.657904743305</v>
+        <v>1500.192929592385</v>
       </c>
       <c r="H3" t="n">
-        <v>8.237654879999997</v>
+        <v>7.585505056345466</v>
       </c>
       <c r="I3" t="n">
-        <v>1499.657904743305</v>
+        <v>1500.192929592385</v>
       </c>
       <c r="J3" t="n">
-        <v>8.239754922959511</v>
+        <v>8.570364869034156</v>
       </c>
       <c r="K3" t="n">
-        <v>1499.657904743305</v>
+        <v>1500.192929592385</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="n">
+      <c r="A4" s="3" t="n">
         <v>49675</v>
       </c>
       <c r="B4" t="n">
-        <v>8.089573475596609</v>
+        <v>8.570364869034156</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -579,33 +580,33 @@
         <v>0.003</v>
       </c>
       <c r="E4" t="n">
-        <v>1499.657904743305</v>
+        <v>1500.192929592385</v>
       </c>
       <c r="F4" t="n">
-        <v>8.089573475596609</v>
+        <v>7.578689065828083</v>
       </c>
       <c r="G4" t="n">
-        <v>1499.657904743305</v>
+        <v>1500.192929592385</v>
       </c>
       <c r="H4" t="n">
-        <v>8.237654879999997</v>
+        <v>7.585505056345467</v>
       </c>
       <c r="I4" t="n">
-        <v>1499.657904743305</v>
+        <v>1500.192929592385</v>
       </c>
       <c r="J4" t="n">
-        <v>8.239754922959511</v>
+        <v>8.570364869034156</v>
       </c>
       <c r="K4" t="n">
-        <v>1499.657904743305</v>
+        <v>1500.192929592385</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="n">
+      <c r="A5" s="3" t="n">
         <v>51502</v>
       </c>
       <c r="B5" t="n">
-        <v>8.089573475596609</v>
+        <v>8.570364869034156</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -616,33 +617,33 @@
         <v>0.003</v>
       </c>
       <c r="E5" t="n">
-        <v>1499.657904743305</v>
+        <v>1500.192929592385</v>
       </c>
       <c r="F5" t="n">
-        <v>8.089573475596609</v>
+        <v>7.810995102943164</v>
       </c>
       <c r="G5" t="n">
-        <v>1499.657904743305</v>
+        <v>1500.192929592385</v>
       </c>
       <c r="H5" t="n">
-        <v>8.456386862090252</v>
+        <v>7.783120634920661</v>
       </c>
       <c r="I5" t="n">
-        <v>1499.657904743305</v>
+        <v>1500.192929592385</v>
       </c>
       <c r="J5" t="n">
-        <v>8.456386862090255</v>
+        <v>8.570364869034156</v>
       </c>
       <c r="K5" t="n">
-        <v>1499.657904743305</v>
+        <v>1500.192929592385</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="n">
+      <c r="A6" s="3" t="n">
         <v>53328</v>
       </c>
       <c r="B6" t="n">
-        <v>8.089573475596609</v>
+        <v>8.570364869034156</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -653,29 +654,29 @@
         <v>0.003</v>
       </c>
       <c r="E6" t="n">
-        <v>1499.657904743305</v>
+        <v>1500.192929592385</v>
       </c>
       <c r="F6" t="n">
-        <v>8.089573475596609</v>
+        <v>7.810995102943164</v>
       </c>
       <c r="G6" t="n">
-        <v>1499.657904743305</v>
+        <v>1500.192929592385</v>
       </c>
       <c r="H6" t="n">
-        <v>8.456386862090252</v>
+        <v>7.783120634920661</v>
       </c>
       <c r="I6" t="n">
-        <v>1499.657904743305</v>
+        <v>1500.192929592385</v>
       </c>
       <c r="J6" t="n">
-        <v>8.456386862090252</v>
+        <v>8.570364869034156</v>
       </c>
       <c r="K6" t="n">
-        <v>1499.657904743305</v>
+        <v>1500.192929592385</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="n">
+      <c r="A7" s="3" t="n">
         <v>46023</v>
       </c>
       <c r="B7" t="n">
@@ -690,29 +691,29 @@
         <v>2</v>
       </c>
       <c r="E7" t="n">
-        <v>2.249486857114957</v>
+        <v>1.083577073379877</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>2.249486857114957</v>
+        <v>2.250289394388578</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>1.083190629310773</v>
+        <v>2.250289394388578</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>1.083190629310773</v>
+        <v>1.083577073379877</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="n">
+      <c r="A8" s="3" t="n">
         <v>47849</v>
       </c>
       <c r="B8" t="n">
@@ -727,29 +728,29 @@
         <v>2</v>
       </c>
       <c r="E8" t="n">
-        <v>2.249486857114957</v>
+        <v>1.543327622275662</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>2.249486857114957</v>
+        <v>2.250289394388578</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>1.542777213983567</v>
+        <v>2.250289394388578</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>1.542777213983567</v>
+        <v>1.543327622275662</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="n">
+      <c r="A9" s="3" t="n">
         <v>49675</v>
       </c>
       <c r="B9" t="n">
@@ -764,29 +765,29 @@
         <v>2</v>
       </c>
       <c r="E9" t="n">
-        <v>2.249486857114957</v>
+        <v>1.774716894167666</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>2.249486857114957</v>
+        <v>2.250289394388578</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>1.77408396381602</v>
+        <v>2.250289394388578</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>1.77408396381602</v>
+        <v>1.774716894167666</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="n">
+      <c r="A10" s="3" t="n">
         <v>51502</v>
       </c>
       <c r="B10" t="n">
@@ -801,29 +802,29 @@
         <v>2</v>
       </c>
       <c r="E10" t="n">
-        <v>2.249486857114957</v>
+        <v>1.905727440522057</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>2.249486857114957</v>
+        <v>2.250289394388578</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>1.90504778691475</v>
+        <v>2.250289394388578</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>1.90504778691475</v>
+        <v>1.905727440522057</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="n">
+      <c r="A11" s="3" t="n">
         <v>53328</v>
       </c>
       <c r="B11" t="n">
@@ -838,33 +839,33 @@
         <v>2</v>
       </c>
       <c r="E11" t="n">
-        <v>2.249486857114957</v>
+        <v>1.986587163207542</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>2.249486857114957</v>
+        <v>2.250289394388578</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>1.985878672002035</v>
+        <v>2.250289394388578</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>1.985878672002035</v>
+        <v>1.986587163207542</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="n">
+      <c r="A12" s="3" t="n">
         <v>46023</v>
       </c>
       <c r="B12" t="n">
-        <v>0.000796075891764706</v>
+        <v>0.0008306878870588232</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -878,30 +879,30 @@
         <v>1</v>
       </c>
       <c r="F12" t="n">
-        <v>0.000796075891764706</v>
+        <v>0.0008306878870588232</v>
       </c>
       <c r="G12" t="n">
         <v>1</v>
       </c>
       <c r="H12" t="n">
-        <v>0.0007960758917647056</v>
+        <v>0.0008306878870588232</v>
       </c>
       <c r="I12" t="n">
         <v>1</v>
       </c>
       <c r="J12" t="n">
-        <v>0.000796075891764706</v>
+        <v>0.0008306878870588232</v>
       </c>
       <c r="K12" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="n">
+      <c r="A13" s="3" t="n">
         <v>47849</v>
       </c>
       <c r="B13" t="n">
-        <v>0.000796075891764706</v>
+        <v>0.0008306878870588232</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -915,30 +916,30 @@
         <v>1</v>
       </c>
       <c r="F13" t="n">
-        <v>0.000796075891764706</v>
+        <v>0.0008306878870588232</v>
       </c>
       <c r="G13" t="n">
         <v>1</v>
       </c>
       <c r="H13" t="n">
-        <v>0.0007960758917647055</v>
+        <v>0.0008306878870588232</v>
       </c>
       <c r="I13" t="n">
         <v>1</v>
       </c>
       <c r="J13" t="n">
-        <v>0.000796075891764706</v>
+        <v>0.0008306878870588232</v>
       </c>
       <c r="K13" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="n">
+      <c r="A14" s="3" t="n">
         <v>49675</v>
       </c>
       <c r="B14" t="n">
-        <v>0.000796075891764706</v>
+        <v>0.0008306878870588232</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -952,30 +953,30 @@
         <v>1</v>
       </c>
       <c r="F14" t="n">
-        <v>0.000796075891764706</v>
+        <v>0.0008306878870588232</v>
       </c>
       <c r="G14" t="n">
         <v>1</v>
       </c>
       <c r="H14" t="n">
-        <v>0.0007960758917647056</v>
+        <v>0.0008306878870588232</v>
       </c>
       <c r="I14" t="n">
         <v>1</v>
       </c>
       <c r="J14" t="n">
-        <v>0.000796075891764706</v>
+        <v>0.0008306878870588232</v>
       </c>
       <c r="K14" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="n">
+      <c r="A15" s="3" t="n">
         <v>51502</v>
       </c>
       <c r="B15" t="n">
-        <v>0.000804214578772092</v>
+        <v>0.0008306878870588232</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -989,7 +990,7 @@
         <v>1</v>
       </c>
       <c r="F15" t="n">
-        <v>0.0008044948377291027</v>
+        <v>0.0008306878870588232</v>
       </c>
       <c r="G15" t="n">
         <v>1</v>
@@ -1008,11 +1009,11 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="n">
+      <c r="A16" s="3" t="n">
         <v>53328</v>
       </c>
       <c r="B16" t="n">
-        <v>0.000804214578772092</v>
+        <v>0.0008306878870588232</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -1026,7 +1027,7 @@
         <v>1</v>
       </c>
       <c r="F16" t="n">
-        <v>0.0008044948377291027</v>
+        <v>0.0008306878870588232</v>
       </c>
       <c r="G16" t="n">
         <v>1</v>
@@ -1045,11 +1046,11 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="n">
+      <c r="A17" s="3" t="n">
         <v>46023</v>
       </c>
       <c r="B17" t="n">
-        <v>0.02453708502392657</v>
+        <v>0.05464918343696924</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -1063,30 +1064,30 @@
         <v>0.1235648232</v>
       </c>
       <c r="F17" t="n">
-        <v>0.02439528173112746</v>
+        <v>0.05464918343696901</v>
       </c>
       <c r="G17" t="n">
         <v>0.1235648232</v>
       </c>
       <c r="H17" t="n">
-        <v>0.02439528173112744</v>
+        <v>0.05464918343696901</v>
       </c>
       <c r="I17" t="n">
         <v>0.1235648232</v>
       </c>
       <c r="J17" t="n">
-        <v>0.02333149854785316</v>
+        <v>0.05464918343696924</v>
       </c>
       <c r="K17" t="n">
         <v>0.1235648232</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="n">
+      <c r="A18" s="3" t="n">
         <v>47849</v>
       </c>
       <c r="B18" t="n">
-        <v>0.02453708502392657</v>
+        <v>0.05464918343696924</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -1100,30 +1101,30 @@
         <v>0.1235648232</v>
       </c>
       <c r="F18" t="n">
-        <v>0.02439528173112746</v>
+        <v>0.05464918343696901</v>
       </c>
       <c r="G18" t="n">
         <v>0.1235648232</v>
       </c>
       <c r="H18" t="n">
-        <v>0.02439528173112744</v>
+        <v>0.05464918343696901</v>
       </c>
       <c r="I18" t="n">
         <v>0.1235648232</v>
       </c>
       <c r="J18" t="n">
-        <v>0.02333149854785316</v>
+        <v>0.05464918343696924</v>
       </c>
       <c r="K18" t="n">
         <v>0.1235648232</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="n">
+      <c r="A19" s="3" t="n">
         <v>49675</v>
       </c>
       <c r="B19" t="n">
-        <v>0.02453708502392657</v>
+        <v>0.05464918343696924</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -1137,30 +1138,30 @@
         <v>0.1235648232</v>
       </c>
       <c r="F19" t="n">
-        <v>0.02439528173112746</v>
+        <v>0.05464918343696901</v>
       </c>
       <c r="G19" t="n">
         <v>0.1235648232</v>
       </c>
       <c r="H19" t="n">
-        <v>0.02439528173112744</v>
+        <v>0.05464918343696901</v>
       </c>
       <c r="I19" t="n">
         <v>0.1235648232</v>
       </c>
       <c r="J19" t="n">
-        <v>0.02333149854785316</v>
+        <v>0.05464918343696924</v>
       </c>
       <c r="K19" t="n">
         <v>0.1235648232</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="n">
+      <c r="A20" s="3" t="n">
         <v>51502</v>
       </c>
       <c r="B20" t="n">
-        <v>0.01384536250546523</v>
+        <v>0.02377320155791523</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -1174,30 +1175,30 @@
         <v>0.1235648232</v>
       </c>
       <c r="F20" t="n">
-        <v>0.01381558499128286</v>
+        <v>0.02377320155791523</v>
       </c>
       <c r="G20" t="n">
         <v>0.1235648232</v>
       </c>
       <c r="H20" t="n">
-        <v>0.01103257350000004</v>
+        <v>0.02377320155791523</v>
       </c>
       <c r="I20" t="n">
         <v>0.1235648232</v>
       </c>
       <c r="J20" t="n">
-        <v>0.01103257350000004</v>
+        <v>0.02377320155791523</v>
       </c>
       <c r="K20" t="n">
         <v>0.1235648232</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="n">
+      <c r="A21" s="3" t="n">
         <v>53328</v>
       </c>
       <c r="B21" t="n">
-        <v>0.01384536250546523</v>
+        <v>0.02377320155791523</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -1211,26 +1212,26 @@
         <v>0.1235648232</v>
       </c>
       <c r="F21" t="n">
-        <v>0.01381558499128286</v>
+        <v>0.02377320155791523</v>
       </c>
       <c r="G21" t="n">
         <v>0.1235648232</v>
       </c>
       <c r="H21" t="n">
-        <v>0.01103257350000004</v>
+        <v>0.02377320155791523</v>
       </c>
       <c r="I21" t="n">
         <v>0.1235648232</v>
       </c>
       <c r="J21" t="n">
-        <v>0.01103257350000004</v>
+        <v>0.02377320155791523</v>
       </c>
       <c r="K21" t="n">
         <v>0.1235648232</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="n">
+      <c r="A22" s="3" t="n">
         <v>46023</v>
       </c>
       <c r="B22" t="n">
@@ -1267,7 +1268,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="n">
+      <c r="A23" s="3" t="n">
         <v>47849</v>
       </c>
       <c r="B23" t="n">
@@ -1304,7 +1305,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="n">
+      <c r="A24" s="3" t="n">
         <v>49675</v>
       </c>
       <c r="B24" t="n">
@@ -1341,7 +1342,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="n">
+      <c r="A25" s="3" t="n">
         <v>51502</v>
       </c>
       <c r="B25" t="n">
@@ -1378,7 +1379,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="n">
+      <c r="A26" s="3" t="n">
         <v>53328</v>
       </c>
       <c r="B26" t="n">
@@ -1415,7 +1416,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="n">
+      <c r="A27" s="3" t="n">
         <v>46023</v>
       </c>
       <c r="B27" t="n">
@@ -1452,7 +1453,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="n">
+      <c r="A28" s="3" t="n">
         <v>47849</v>
       </c>
       <c r="B28" t="n">
@@ -1489,7 +1490,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="n">
+      <c r="A29" s="3" t="n">
         <v>49675</v>
       </c>
       <c r="B29" t="n">
@@ -1526,7 +1527,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="2" t="n">
+      <c r="A30" s="3" t="n">
         <v>51502</v>
       </c>
       <c r="B30" t="n">
@@ -1563,7 +1564,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="2" t="n">
+      <c r="A31" s="3" t="n">
         <v>53328</v>
       </c>
       <c r="B31" t="n">
@@ -1600,7 +1601,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="2" t="n">
+      <c r="A32" s="3" t="n">
         <v>46023</v>
       </c>
       <c r="B32" t="n">
@@ -1637,7 +1638,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="2" t="n">
+      <c r="A33" s="3" t="n">
         <v>47849</v>
       </c>
       <c r="B33" t="n">
@@ -1674,7 +1675,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="2" t="n">
+      <c r="A34" s="3" t="n">
         <v>49675</v>
       </c>
       <c r="B34" t="n">
@@ -1711,7 +1712,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="2" t="n">
+      <c r="A35" s="3" t="n">
         <v>51502</v>
       </c>
       <c r="B35" t="n">
@@ -1748,7 +1749,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="2" t="n">
+      <c r="A36" s="3" t="n">
         <v>53328</v>
       </c>
       <c r="B36" t="n">
@@ -1785,7 +1786,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="2" t="n">
+      <c r="A37" s="3" t="n">
         <v>46023</v>
       </c>
       <c r="B37" t="n">
@@ -1822,7 +1823,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="2" t="n">
+      <c r="A38" s="3" t="n">
         <v>47849</v>
       </c>
       <c r="B38" t="n">
@@ -1859,7 +1860,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="2" t="n">
+      <c r="A39" s="3" t="n">
         <v>49675</v>
       </c>
       <c r="B39" t="n">
@@ -1896,7 +1897,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="2" t="n">
+      <c r="A40" s="3" t="n">
         <v>51502</v>
       </c>
       <c r="B40" t="n">
@@ -1933,7 +1934,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="2" t="n">
+      <c r="A41" s="3" t="n">
         <v>53328</v>
       </c>
       <c r="B41" t="n">
@@ -1970,7 +1971,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="2" t="n">
+      <c r="A42" s="3" t="n">
         <v>46023</v>
       </c>
       <c r="B42" t="n">
@@ -1985,7 +1986,7 @@
         <v>0.03</v>
       </c>
       <c r="E42" t="n">
-        <v>0.402678944077692</v>
+        <v>0.2046115363271334</v>
       </c>
       <c r="F42" t="n">
         <v>0</v>
@@ -1997,7 +1998,7 @@
         <v>0</v>
       </c>
       <c r="I42" t="n">
-        <v>0.2046115363271334</v>
+        <v>0.402678944077692</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -2007,7 +2008,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="2" t="n">
+      <c r="A43" s="3" t="n">
         <v>47849</v>
       </c>
       <c r="B43" t="n">
@@ -2022,7 +2023,7 @@
         <v>0.03</v>
       </c>
       <c r="E43" t="n">
-        <v>0.402678944077692</v>
+        <v>0.2871971342961154</v>
       </c>
       <c r="F43" t="n">
         <v>0</v>
@@ -2034,7 +2035,7 @@
         <v>0</v>
       </c>
       <c r="I43" t="n">
-        <v>0.2871971342961154</v>
+        <v>0.402678944077692</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -2044,7 +2045,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="2" t="n">
+      <c r="A44" s="3" t="n">
         <v>49675</v>
       </c>
       <c r="B44" t="n">
@@ -2059,7 +2060,7 @@
         <v>0.03</v>
       </c>
       <c r="E44" t="n">
-        <v>0.402678944077692</v>
+        <v>0.3272143951258143</v>
       </c>
       <c r="F44" t="n">
         <v>0</v>
@@ -2071,7 +2072,7 @@
         <v>0</v>
       </c>
       <c r="I44" t="n">
-        <v>0.3272143951258143</v>
+        <v>0.402678944077692</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -2081,7 +2082,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="2" t="n">
+      <c r="A45" s="3" t="n">
         <v>51502</v>
       </c>
       <c r="B45" t="n">
@@ -2096,7 +2097,7 @@
         <v>0.03</v>
       </c>
       <c r="E45" t="n">
-        <v>0.402678944077692</v>
+        <v>0.3492170049785441</v>
       </c>
       <c r="F45" t="n">
         <v>0</v>
@@ -2108,7 +2109,7 @@
         <v>0</v>
       </c>
       <c r="I45" t="n">
-        <v>0.3492170049785441</v>
+        <v>0.402678944077692</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -2118,11 +2119,11 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="2" t="n">
+      <c r="A46" s="3" t="n">
         <v>53328</v>
       </c>
       <c r="B46" t="n">
-        <v>0</v>
+        <v>0.3667758145154252</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -2133,7 +2134,7 @@
         <v>0.03</v>
       </c>
       <c r="E46" t="n">
-        <v>0.402678944077692</v>
+        <v>0.3624849667870516</v>
       </c>
       <c r="F46" t="n">
         <v>0</v>
@@ -2145,7 +2146,7 @@
         <v>0</v>
       </c>
       <c r="I46" t="n">
-        <v>0.3624849667870516</v>
+        <v>0.402678944077692</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -2155,7 +2156,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="2" t="n">
+      <c r="A47" s="3" t="n">
         <v>46023</v>
       </c>
       <c r="B47" t="n">
@@ -2170,33 +2171,33 @@
         <v>0.08</v>
       </c>
       <c r="E47" t="n">
-        <v>0.4599029927197631</v>
+        <v>0.6014116058643056</v>
       </c>
       <c r="F47" t="n">
         <v>0</v>
       </c>
       <c r="G47" t="n">
-        <v>0.4599029927197631</v>
+        <v>0.6014116058643056</v>
       </c>
       <c r="H47" t="n">
         <v>0</v>
       </c>
       <c r="I47" t="n">
-        <v>0.4599029927197631</v>
+        <v>0.6014116058643056</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
       </c>
       <c r="K47" t="n">
-        <v>0.4599029927197631</v>
+        <v>0.6014116058643056</v>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="2" t="n">
+      <c r="A48" s="3" t="n">
         <v>47849</v>
       </c>
       <c r="B48" t="n">
-        <v>0.06702276814896589</v>
+        <v>0</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -2207,33 +2208,33 @@
         <v>0.08</v>
       </c>
       <c r="E48" t="n">
-        <v>0.4599029927197631</v>
+        <v>0.6014116058643056</v>
       </c>
       <c r="F48" t="n">
-        <v>0.07167423014462887</v>
+        <v>0</v>
       </c>
       <c r="G48" t="n">
-        <v>0.4599029927197631</v>
+        <v>0.6014116058643056</v>
       </c>
       <c r="H48" t="n">
-        <v>0.06818611592944919</v>
+        <v>0</v>
       </c>
       <c r="I48" t="n">
-        <v>0.4599029927197631</v>
+        <v>0.6014116058643056</v>
       </c>
       <c r="J48" t="n">
-        <v>0.07098928394540456</v>
+        <v>0</v>
       </c>
       <c r="K48" t="n">
-        <v>0.4599029927197631</v>
+        <v>0.6014116058643056</v>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="2" t="n">
+      <c r="A49" s="3" t="n">
         <v>49675</v>
       </c>
       <c r="B49" t="n">
-        <v>0.06702276814896589</v>
+        <v>0</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -2244,33 +2245,33 @@
         <v>0.08</v>
       </c>
       <c r="E49" t="n">
-        <v>0.4599029927197631</v>
+        <v>0.6014116058643056</v>
       </c>
       <c r="F49" t="n">
-        <v>0.07167423014462887</v>
+        <v>0</v>
       </c>
       <c r="G49" t="n">
-        <v>0.4599029927197631</v>
+        <v>0.6014116058643056</v>
       </c>
       <c r="H49" t="n">
-        <v>0.06818611592944919</v>
+        <v>0</v>
       </c>
       <c r="I49" t="n">
-        <v>0.4599029927197631</v>
+        <v>0.6014116058643056</v>
       </c>
       <c r="J49" t="n">
-        <v>0.07098928394540456</v>
+        <v>0</v>
       </c>
       <c r="K49" t="n">
-        <v>0.4599029927197631</v>
+        <v>0.6014116058643056</v>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="2" t="n">
+      <c r="A50" s="3" t="n">
         <v>51502</v>
       </c>
       <c r="B50" t="n">
-        <v>0.06702276814896589</v>
+        <v>0</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -2281,29 +2282,29 @@
         <v>0.08</v>
       </c>
       <c r="E50" t="n">
-        <v>0.4599029927197631</v>
+        <v>0.6014116058643056</v>
       </c>
       <c r="F50" t="n">
-        <v>0.07167423014462887</v>
+        <v>0</v>
       </c>
       <c r="G50" t="n">
-        <v>0.4599029927197631</v>
+        <v>0.6014116058643056</v>
       </c>
       <c r="H50" t="n">
-        <v>0.06818611592944919</v>
+        <v>0</v>
       </c>
       <c r="I50" t="n">
-        <v>0.4599029927197631</v>
+        <v>0.6014116058643056</v>
       </c>
       <c r="J50" t="n">
-        <v>0.07098928394540456</v>
+        <v>0</v>
       </c>
       <c r="K50" t="n">
-        <v>0.4599029927197631</v>
+        <v>0.6014116058643056</v>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="2" t="n">
+      <c r="A51" s="3" t="n">
         <v>53328</v>
       </c>
       <c r="B51" t="n">
@@ -2318,33 +2319,33 @@
         <v>0.08</v>
       </c>
       <c r="E51" t="n">
-        <v>0.4599029927197631</v>
+        <v>0.6014116058643056</v>
       </c>
       <c r="F51" t="n">
         <v>0</v>
       </c>
       <c r="G51" t="n">
-        <v>0.4599029927197631</v>
+        <v>0.6014116058643056</v>
       </c>
       <c r="H51" t="n">
         <v>0</v>
       </c>
       <c r="I51" t="n">
-        <v>0.4599029927197631</v>
+        <v>0.6014116058643056</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
       </c>
       <c r="K51" t="n">
-        <v>0.4599029927197631</v>
+        <v>0.6014116058643056</v>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="2" t="n">
+      <c r="A52" s="3" t="n">
         <v>46023</v>
       </c>
       <c r="B52" t="n">
-        <v>0.002004806806213684</v>
+        <v>0.0841929480131922</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -2355,33 +2356,33 @@
         <v>0.08</v>
       </c>
       <c r="E52" t="n">
-        <v>0.4599029927197631</v>
+        <v>0.1323240299819102</v>
       </c>
       <c r="F52" t="n">
-        <v>0.05013133668662601</v>
+        <v>0.08502985723903585</v>
       </c>
       <c r="G52" t="n">
-        <v>0.4599029927197631</v>
+        <v>0.6014116058643056</v>
       </c>
       <c r="H52" t="n">
-        <v>0.02505216113119287</v>
+        <v>0.0841929480131922</v>
       </c>
       <c r="I52" t="n">
-        <v>0.1011889641038137</v>
+        <v>0.6014116058643056</v>
       </c>
       <c r="J52" t="n">
-        <v>0.050131336686626</v>
+        <v>0.08394654034242725</v>
       </c>
       <c r="K52" t="n">
-        <v>0.1011889641038137</v>
+        <v>0.1323240299819102</v>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="2" t="n">
+      <c r="A53" s="3" t="n">
         <v>47849</v>
       </c>
       <c r="B53" t="n">
-        <v>0.00261410707679149</v>
+        <v>0.08821042176137427</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -2392,33 +2393,33 @@
         <v>0.08</v>
       </c>
       <c r="E53" t="n">
-        <v>0.4599029927197631</v>
+        <v>0.2154936369329378</v>
       </c>
       <c r="F53" t="n">
-        <v>0.05276222932438859</v>
+        <v>0.08973961729908206</v>
       </c>
       <c r="G53" t="n">
-        <v>0.4599029927197631</v>
+        <v>0.6014116058643056</v>
       </c>
       <c r="H53" t="n">
-        <v>0.02661349432706812</v>
+        <v>0.08972557654522417</v>
       </c>
       <c r="I53" t="n">
-        <v>0.1647892517722465</v>
+        <v>0.6014116058643056</v>
       </c>
       <c r="J53" t="n">
-        <v>0.0527714520574223</v>
+        <v>0.0878704725131922</v>
       </c>
       <c r="K53" t="n">
-        <v>0.1647892517722465</v>
+        <v>0.2154936369329378</v>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="2" t="n">
+      <c r="A54" s="3" t="n">
         <v>49675</v>
       </c>
       <c r="B54" t="n">
-        <v>0.00261410707679149</v>
+        <v>0.08821042176137427</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -2429,33 +2430,33 @@
         <v>0.08</v>
       </c>
       <c r="E54" t="n">
-        <v>0.4599029927197631</v>
+        <v>0.2711964643509661</v>
       </c>
       <c r="F54" t="n">
-        <v>0.05276222932438859</v>
+        <v>0.08973961729908206</v>
       </c>
       <c r="G54" t="n">
-        <v>0.4599029927197631</v>
+        <v>0.6014116058643056</v>
       </c>
       <c r="H54" t="n">
-        <v>0.02661349432706812</v>
+        <v>0.08972557654522417</v>
       </c>
       <c r="I54" t="n">
-        <v>0.2073855315625035</v>
+        <v>0.6014116058643056</v>
       </c>
       <c r="J54" t="n">
-        <v>0.0527714520574223</v>
+        <v>0.0878704725131922</v>
       </c>
       <c r="K54" t="n">
-        <v>0.2073855315625035</v>
+        <v>0.2711964643509661</v>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="2" t="n">
+      <c r="A55" s="3" t="n">
         <v>51502</v>
       </c>
       <c r="B55" t="n">
-        <v>0.06766280487681638</v>
+        <v>0.08114859928711876</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -2466,33 +2467,33 @@
         <v>0.08</v>
       </c>
       <c r="E55" t="n">
-        <v>0.4599029927197631</v>
+        <v>0.3104699533606</v>
       </c>
       <c r="F55" t="n">
-        <v>0.06301134288115338</v>
+        <v>0.0823541857631922</v>
       </c>
       <c r="G55" t="n">
-        <v>0.4599029927197631</v>
+        <v>0.6014116058643056</v>
       </c>
       <c r="H55" t="n">
-        <v>0.06478001934714414</v>
+        <v>0.08114859928711876</v>
       </c>
       <c r="I55" t="n">
-        <v>0.2374181996286941</v>
+        <v>0.6014116058643056</v>
       </c>
       <c r="J55" t="n">
-        <v>0.06197685133118875</v>
+        <v>0.08229131555511543</v>
       </c>
       <c r="K55" t="n">
-        <v>0.2374181996286941</v>
+        <v>0.3104699533606</v>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="2" t="n">
+      <c r="A56" s="3" t="n">
         <v>53328</v>
       </c>
       <c r="B56" t="n">
-        <v>0.09060064927557095</v>
+        <v>0.08543131419974906</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -2503,29 +2504,29 @@
         <v>0.08</v>
       </c>
       <c r="E56" t="n">
-        <v>0.4599029927197631</v>
+        <v>0.3393165135782333</v>
       </c>
       <c r="F56" t="n">
-        <v>0.08971570758075378</v>
+        <v>0.08851617587476523</v>
       </c>
       <c r="G56" t="n">
-        <v>0.4599029927197631</v>
+        <v>0.6014116058643056</v>
       </c>
       <c r="H56" t="n">
-        <v>0.09034019286726226</v>
+        <v>0.08666488603711876</v>
       </c>
       <c r="I56" t="n">
-        <v>0.2594773339127666</v>
+        <v>0.6014116058643056</v>
       </c>
       <c r="J56" t="n">
-        <v>0.08979848485815264</v>
+        <v>0.08816840369615396</v>
       </c>
       <c r="K56" t="n">
-        <v>0.2594773339127666</v>
+        <v>0.3393165135782333</v>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="2" t="n">
+      <c r="A57" s="3" t="n">
         <v>46023</v>
       </c>
       <c r="B57" t="n">
@@ -2540,29 +2541,29 @@
         <v>0.08</v>
       </c>
       <c r="E57" t="n">
-        <v>0.4599029927197631</v>
+        <v>0.1323240299819102</v>
       </c>
       <c r="F57" t="n">
         <v>0</v>
       </c>
       <c r="G57" t="n">
-        <v>0.4599029927197631</v>
+        <v>0.6014116058643056</v>
       </c>
       <c r="H57" t="n">
         <v>0</v>
       </c>
       <c r="I57" t="n">
-        <v>0.1011889641038137</v>
+        <v>0.6014116058643056</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
       </c>
       <c r="K57" t="n">
-        <v>0.1011889641038137</v>
+        <v>0.1323240299819102</v>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="2" t="n">
+      <c r="A58" s="3" t="n">
         <v>47849</v>
       </c>
       <c r="B58" t="n">
@@ -2577,29 +2578,29 @@
         <v>0.08</v>
       </c>
       <c r="E58" t="n">
-        <v>0.4599029927197631</v>
+        <v>0.2154936369329378</v>
       </c>
       <c r="F58" t="n">
         <v>0</v>
       </c>
       <c r="G58" t="n">
-        <v>0.4599029927197631</v>
+        <v>0.6014116058643056</v>
       </c>
       <c r="H58" t="n">
         <v>0</v>
       </c>
       <c r="I58" t="n">
-        <v>0.1647892517722465</v>
+        <v>0.6014116058643056</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
       </c>
       <c r="K58" t="n">
-        <v>0.1647892517722465</v>
+        <v>0.2154936369329378</v>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="2" t="n">
+      <c r="A59" s="3" t="n">
         <v>49675</v>
       </c>
       <c r="B59" t="n">
@@ -2614,29 +2615,29 @@
         <v>0.08</v>
       </c>
       <c r="E59" t="n">
-        <v>0.4599029927197631</v>
+        <v>0.2711964643509661</v>
       </c>
       <c r="F59" t="n">
         <v>0</v>
       </c>
       <c r="G59" t="n">
-        <v>0.4599029927197631</v>
+        <v>0.6014116058643056</v>
       </c>
       <c r="H59" t="n">
         <v>0</v>
       </c>
       <c r="I59" t="n">
-        <v>0.2073855315625035</v>
+        <v>0.6014116058643056</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
       </c>
       <c r="K59" t="n">
-        <v>0.2073855315625035</v>
+        <v>0.2711964643509661</v>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="2" t="n">
+      <c r="A60" s="3" t="n">
         <v>51502</v>
       </c>
       <c r="B60" t="n">
@@ -2651,29 +2652,29 @@
         <v>0.08</v>
       </c>
       <c r="E60" t="n">
-        <v>0.4599029927197631</v>
+        <v>0.3104699533606</v>
       </c>
       <c r="F60" t="n">
         <v>0</v>
       </c>
       <c r="G60" t="n">
-        <v>0.4599029927197631</v>
+        <v>0.6014116058643056</v>
       </c>
       <c r="H60" t="n">
         <v>0</v>
       </c>
       <c r="I60" t="n">
-        <v>0.2374181996286941</v>
+        <v>0.6014116058643056</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
       </c>
       <c r="K60" t="n">
-        <v>0.2374181996286941</v>
+        <v>0.3104699533606</v>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="2" t="n">
+      <c r="A61" s="3" t="n">
         <v>53328</v>
       </c>
       <c r="B61" t="n">
@@ -2688,29 +2689,29 @@
         <v>0.08</v>
       </c>
       <c r="E61" t="n">
-        <v>0.4599029927197631</v>
+        <v>0.3393165135782333</v>
       </c>
       <c r="F61" t="n">
         <v>0</v>
       </c>
       <c r="G61" t="n">
-        <v>0.4599029927197631</v>
+        <v>0.6014116058643056</v>
       </c>
       <c r="H61" t="n">
         <v>0</v>
       </c>
       <c r="I61" t="n">
-        <v>0.2594773339127666</v>
+        <v>0.6014116058643056</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
       </c>
       <c r="K61" t="n">
-        <v>0.2594773339127666</v>
+        <v>0.3393165135782333</v>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="2" t="n">
+      <c r="A62" s="3" t="n">
         <v>46023</v>
       </c>
       <c r="B62" t="n">
@@ -2725,33 +2726,33 @@
         <v>0.08</v>
       </c>
       <c r="E62" t="n">
-        <v>0.4599029927197631</v>
+        <v>0.6014116058643056</v>
       </c>
       <c r="F62" t="n">
         <v>0</v>
       </c>
       <c r="G62" t="n">
-        <v>0.4599029927197631</v>
+        <v>0.6014116058643056</v>
       </c>
       <c r="H62" t="n">
         <v>0</v>
       </c>
       <c r="I62" t="n">
-        <v>0.4599029927197631</v>
+        <v>0.6014116058643056</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
       </c>
       <c r="K62" t="n">
-        <v>0.4599029927197631</v>
+        <v>0.6014116058643056</v>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="2" t="n">
+      <c r="A63" s="3" t="n">
         <v>47849</v>
       </c>
       <c r="B63" t="n">
-        <v>0.02025676728588986</v>
+        <v>0.03876591992944924</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -2762,33 +2763,33 @@
         <v>0.08</v>
       </c>
       <c r="E63" t="n">
-        <v>0.4599029927197631</v>
+        <v>0.6014116058643056</v>
       </c>
       <c r="F63" t="n">
-        <v>0.02025676728588987</v>
+        <v>0.04097449930278309</v>
       </c>
       <c r="G63" t="n">
-        <v>0.4599029927197631</v>
+        <v>0.6014116058643056</v>
       </c>
       <c r="H63" t="n">
-        <v>0.02025676728588983</v>
+        <v>0.04186729551757756</v>
       </c>
       <c r="I63" t="n">
-        <v>0.4599029927197631</v>
+        <v>0.6014116058643056</v>
       </c>
       <c r="J63" t="n">
-        <v>0.02025676728588984</v>
+        <v>0.03708146432864604</v>
       </c>
       <c r="K63" t="n">
-        <v>0.4599029927197631</v>
+        <v>0.6014116058643056</v>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="2" t="n">
+      <c r="A64" s="3" t="n">
         <v>49675</v>
       </c>
       <c r="B64" t="n">
-        <v>0.02025676728588986</v>
+        <v>0.03876591992944924</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -2799,33 +2800,33 @@
         <v>0.08</v>
       </c>
       <c r="E64" t="n">
-        <v>0.4599029927197631</v>
+        <v>0.6014116058643056</v>
       </c>
       <c r="F64" t="n">
-        <v>0.02025676728588987</v>
+        <v>0.04097449930278309</v>
       </c>
       <c r="G64" t="n">
-        <v>0.4599029927197631</v>
+        <v>0.6014116058643056</v>
       </c>
       <c r="H64" t="n">
-        <v>0.02025676728588983</v>
+        <v>0.04186729551757756</v>
       </c>
       <c r="I64" t="n">
-        <v>0.4599029927197631</v>
+        <v>0.6014116058643056</v>
       </c>
       <c r="J64" t="n">
-        <v>0.02025676728588984</v>
+        <v>0.03708146432864604</v>
       </c>
       <c r="K64" t="n">
-        <v>0.4599029927197631</v>
+        <v>0.6014116058643056</v>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="2" t="n">
+      <c r="A65" s="3" t="n">
         <v>51502</v>
       </c>
       <c r="B65" t="n">
-        <v>0.02025676728588986</v>
+        <v>0.04582774240370474</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -2836,33 +2837,33 @@
         <v>0.08</v>
       </c>
       <c r="E65" t="n">
-        <v>0.4599029927197631</v>
+        <v>0.6014116058643056</v>
       </c>
       <c r="F65" t="n">
-        <v>0.02025676728588987</v>
+        <v>0.04818170170618283</v>
       </c>
       <c r="G65" t="n">
-        <v>0.4599029927197631</v>
+        <v>0.6014116058643056</v>
       </c>
       <c r="H65" t="n">
-        <v>0.02025676728588983</v>
+        <v>0.04951794975111175</v>
       </c>
       <c r="I65" t="n">
-        <v>0.4599029927197631</v>
+        <v>0.6014116058643056</v>
       </c>
       <c r="J65" t="n">
-        <v>0.02025676728588984</v>
+        <v>0.04468502613570808</v>
       </c>
       <c r="K65" t="n">
-        <v>0.4599029927197631</v>
+        <v>0.6014116058643056</v>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="2" t="n">
+      <c r="A66" s="3" t="n">
         <v>53328</v>
       </c>
       <c r="B66" t="n">
-        <v>0.06434169103610117</v>
+        <v>0.04154502749107446</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -2873,29 +2874,29 @@
         <v>0.08</v>
       </c>
       <c r="E66" t="n">
-        <v>0.4599029927197631</v>
+        <v>0.6014116058643056</v>
       </c>
       <c r="F66" t="n">
-        <v>0.06522663273091835</v>
+        <v>0.04201971159460979</v>
       </c>
       <c r="G66" t="n">
-        <v>0.4599029927197631</v>
+        <v>0.6014116058643056</v>
       </c>
       <c r="H66" t="n">
-        <v>0.0628827096952209</v>
+        <v>0.04400166300111176</v>
       </c>
       <c r="I66" t="n">
-        <v>0.4599029927197631</v>
+        <v>0.6014116058643056</v>
       </c>
       <c r="J66" t="n">
-        <v>0.06342441770433054</v>
+        <v>0.03880793799466955</v>
       </c>
       <c r="K66" t="n">
-        <v>0.4599029927197631</v>
+        <v>0.6014116058643056</v>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="2" t="n">
+      <c r="A67" s="3" t="n">
         <v>46023</v>
       </c>
       <c r="B67" t="n">
@@ -2910,29 +2911,29 @@
         <v>0.08</v>
       </c>
       <c r="E67" t="n">
-        <v>0.4599029927197631</v>
+        <v>0.6014116058643056</v>
       </c>
       <c r="F67" t="n">
         <v>0</v>
       </c>
       <c r="G67" t="n">
-        <v>0.4599029927197631</v>
+        <v>0.6014116058643056</v>
       </c>
       <c r="H67" t="n">
         <v>0</v>
       </c>
       <c r="I67" t="n">
-        <v>0.4599029927197631</v>
+        <v>0.6014116058643056</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
       </c>
       <c r="K67" t="n">
-        <v>0.4599029927197631</v>
+        <v>0.6014116058643056</v>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="2" t="n">
+      <c r="A68" s="3" t="n">
         <v>47849</v>
       </c>
       <c r="B68" t="n">
@@ -2947,29 +2948,29 @@
         <v>0.08</v>
       </c>
       <c r="E68" t="n">
-        <v>0.4599029927197631</v>
+        <v>0.6014116058643056</v>
       </c>
       <c r="F68" t="n">
         <v>0</v>
       </c>
       <c r="G68" t="n">
-        <v>0.4599029927197631</v>
+        <v>0.6014116058643056</v>
       </c>
       <c r="H68" t="n">
         <v>0</v>
       </c>
       <c r="I68" t="n">
-        <v>0.4599029927197631</v>
+        <v>0.6014116058643056</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
       </c>
       <c r="K68" t="n">
-        <v>0.4599029927197631</v>
+        <v>0.6014116058643056</v>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="2" t="n">
+      <c r="A69" s="3" t="n">
         <v>49675</v>
       </c>
       <c r="B69" t="n">
@@ -2984,29 +2985,29 @@
         <v>0.08</v>
       </c>
       <c r="E69" t="n">
-        <v>0.4599029927197631</v>
+        <v>0.6014116058643056</v>
       </c>
       <c r="F69" t="n">
         <v>0</v>
       </c>
       <c r="G69" t="n">
-        <v>0.4599029927197631</v>
+        <v>0.6014116058643056</v>
       </c>
       <c r="H69" t="n">
         <v>0</v>
       </c>
       <c r="I69" t="n">
-        <v>0.4599029927197631</v>
+        <v>0.6014116058643056</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
       </c>
       <c r="K69" t="n">
-        <v>0.4599029927197631</v>
+        <v>0.6014116058643056</v>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="2" t="n">
+      <c r="A70" s="3" t="n">
         <v>51502</v>
       </c>
       <c r="B70" t="n">
@@ -3021,29 +3022,29 @@
         <v>0.08</v>
       </c>
       <c r="E70" t="n">
-        <v>0.4599029927197631</v>
+        <v>0.6014116058643056</v>
       </c>
       <c r="F70" t="n">
         <v>0</v>
       </c>
       <c r="G70" t="n">
-        <v>0.4599029927197631</v>
+        <v>0.6014116058643056</v>
       </c>
       <c r="H70" t="n">
         <v>0</v>
       </c>
       <c r="I70" t="n">
-        <v>0.4599029927197631</v>
+        <v>0.6014116058643056</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
       </c>
       <c r="K70" t="n">
-        <v>0.4599029927197631</v>
+        <v>0.6014116058643056</v>
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="2" t="n">
+      <c r="A71" s="3" t="n">
         <v>53328</v>
       </c>
       <c r="B71" t="n">
@@ -3058,29 +3059,29 @@
         <v>0.08</v>
       </c>
       <c r="E71" t="n">
-        <v>0.4599029927197631</v>
+        <v>0.6014116058643056</v>
       </c>
       <c r="F71" t="n">
         <v>0</v>
       </c>
       <c r="G71" t="n">
-        <v>0.4599029927197631</v>
+        <v>0.6014116058643056</v>
       </c>
       <c r="H71" t="n">
         <v>0</v>
       </c>
       <c r="I71" t="n">
-        <v>0.4599029927197631</v>
+        <v>0.6014116058643056</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
       </c>
       <c r="K71" t="n">
-        <v>0.4599029927197631</v>
+        <v>0.6014116058643056</v>
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="2" t="n">
+      <c r="A72" s="3" t="n">
         <v>46023</v>
       </c>
       <c r="B72" t="n">
@@ -3095,29 +3096,29 @@
         <v>0.08</v>
       </c>
       <c r="E72" t="n">
-        <v>0.4599029927197631</v>
+        <v>0.03682040983458015</v>
       </c>
       <c r="F72" t="n">
         <v>0</v>
       </c>
       <c r="G72" t="n">
-        <v>0.4599029927197631</v>
+        <v>0.6014116058643056</v>
       </c>
       <c r="H72" t="n">
         <v>0</v>
       </c>
       <c r="I72" t="n">
-        <v>0.02815678399114953</v>
+        <v>0.6014116058643056</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
       </c>
       <c r="K72" t="n">
-        <v>0.02815678399114953</v>
+        <v>0.03682040983458015</v>
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="2" t="n">
+      <c r="A73" s="3" t="n">
         <v>47849</v>
       </c>
       <c r="B73" t="n">
@@ -3132,29 +3133,29 @@
         <v>0.08</v>
       </c>
       <c r="E73" t="n">
-        <v>0.4599029927197631</v>
+        <v>0.06568130249835975</v>
       </c>
       <c r="F73" t="n">
         <v>0</v>
       </c>
       <c r="G73" t="n">
-        <v>0.4599029927197631</v>
+        <v>0.6014116058643056</v>
       </c>
       <c r="H73" t="n">
         <v>0</v>
       </c>
       <c r="I73" t="n">
-        <v>0.05022687838109863</v>
+        <v>0.6014116058643056</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
       </c>
       <c r="K73" t="n">
-        <v>0.05022687838109863</v>
+        <v>0.06568130249835975</v>
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="2" t="n">
+      <c r="A74" s="3" t="n">
         <v>49675</v>
       </c>
       <c r="B74" t="n">
@@ -3169,29 +3170,29 @@
         <v>0.08</v>
       </c>
       <c r="E74" t="n">
-        <v>0.4599029927197631</v>
+        <v>0.08919625628063554</v>
       </c>
       <c r="F74" t="n">
         <v>0</v>
       </c>
       <c r="G74" t="n">
-        <v>0.4599029927197631</v>
+        <v>0.6014116058643056</v>
       </c>
       <c r="H74" t="n">
         <v>0</v>
       </c>
       <c r="I74" t="n">
-        <v>0.06820890186166248</v>
+        <v>0.6014116058643056</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
       </c>
       <c r="K74" t="n">
-        <v>0.06820890186166248</v>
+        <v>0.08919625628063554</v>
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="2" t="n">
+      <c r="A75" s="3" t="n">
         <v>51502</v>
       </c>
       <c r="B75" t="n">
@@ -3206,29 +3207,29 @@
         <v>0.08</v>
       </c>
       <c r="E75" t="n">
-        <v>0.4599029927197631</v>
+        <v>0.1089050369639545</v>
       </c>
       <c r="F75" t="n">
         <v>0</v>
       </c>
       <c r="G75" t="n">
-        <v>0.4599029927197631</v>
+        <v>0.6014116058643056</v>
       </c>
       <c r="H75" t="n">
         <v>0</v>
       </c>
       <c r="I75" t="n">
-        <v>0.08328032238420052</v>
+        <v>0.6014116058643056</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
       </c>
       <c r="K75" t="n">
-        <v>0.08328032238420052</v>
+        <v>0.1089050369639545</v>
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="2" t="n">
+      <c r="A76" s="3" t="n">
         <v>53328</v>
       </c>
       <c r="B76" t="n">
@@ -3243,33 +3244,33 @@
         <v>0.08</v>
       </c>
       <c r="E76" t="n">
-        <v>0.4599029927197631</v>
+        <v>0.1257467230135668</v>
       </c>
       <c r="F76" t="n">
         <v>0</v>
       </c>
       <c r="G76" t="n">
-        <v>0.4599029927197631</v>
+        <v>0.6014116058643056</v>
       </c>
       <c r="H76" t="n">
         <v>0</v>
       </c>
       <c r="I76" t="n">
-        <v>0.09615925877508052</v>
+        <v>0.6014116058643056</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
       </c>
       <c r="K76" t="n">
-        <v>0.09615925877508052</v>
+        <v>0.1257467230135668</v>
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="2" t="n">
+      <c r="A77" s="3" t="n">
         <v>46023</v>
       </c>
       <c r="B77" t="n">
-        <v>0.0650486978000249</v>
+        <v>0</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -3280,33 +3281,33 @@
         <v>0.08</v>
       </c>
       <c r="E77" t="n">
-        <v>0.4599029927197631</v>
+        <v>0.03682040983458015</v>
       </c>
       <c r="F77" t="n">
-        <v>0.01024911355676481</v>
+        <v>0.0009107054164868193</v>
       </c>
       <c r="G77" t="n">
-        <v>0.4599029927197631</v>
+        <v>0.6014116058643056</v>
       </c>
       <c r="H77" t="n">
-        <v>0.03919183118612408</v>
+        <v>0</v>
       </c>
       <c r="I77" t="n">
-        <v>0.02815678399114953</v>
+        <v>0.6014116058643056</v>
       </c>
       <c r="J77" t="n">
-        <v>0.0102208614884418</v>
+        <v>0.002024404848985258</v>
       </c>
       <c r="K77" t="n">
-        <v>0.02815678399114953</v>
+        <v>0.03682040983458015</v>
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="2" t="n">
+      <c r="A78" s="3" t="n">
         <v>47849</v>
       </c>
       <c r="B78" t="n">
-        <v>0.0650486978000249</v>
+        <v>0</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -3317,33 +3318,33 @@
         <v>0.08</v>
       </c>
       <c r="E78" t="n">
-        <v>0.4599029927197631</v>
+        <v>0.06568130249835975</v>
       </c>
       <c r="F78" t="n">
-        <v>0.01024911355676481</v>
+        <v>0.0009107054164868193</v>
       </c>
       <c r="G78" t="n">
-        <v>0.4599029927197631</v>
+        <v>0.6014116058643056</v>
       </c>
       <c r="H78" t="n">
-        <v>0.03919183118612408</v>
+        <v>0</v>
       </c>
       <c r="I78" t="n">
-        <v>0.05022687838109863</v>
+        <v>0.6014116058643056</v>
       </c>
       <c r="J78" t="n">
-        <v>0.0102208614884418</v>
+        <v>0.002024404848985258</v>
       </c>
       <c r="K78" t="n">
-        <v>0.05022687838109863</v>
+        <v>0.06568130249835975</v>
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="2" t="n">
+      <c r="A79" s="3" t="n">
         <v>49675</v>
       </c>
       <c r="B79" t="n">
-        <v>0.0650486978000249</v>
+        <v>0</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -3354,29 +3355,29 @@
         <v>0.08</v>
       </c>
       <c r="E79" t="n">
-        <v>0.4599029927197631</v>
+        <v>0.08919625628063554</v>
       </c>
       <c r="F79" t="n">
-        <v>0.01024911355676481</v>
+        <v>0.0009107054164868193</v>
       </c>
       <c r="G79" t="n">
-        <v>0.4599029927197631</v>
+        <v>0.6014116058643056</v>
       </c>
       <c r="H79" t="n">
-        <v>0.03919183118612408</v>
+        <v>0</v>
       </c>
       <c r="I79" t="n">
-        <v>0.06820890186166248</v>
+        <v>0.6014116058643056</v>
       </c>
       <c r="J79" t="n">
-        <v>0.0102208614884418</v>
+        <v>0.002024404848985258</v>
       </c>
       <c r="K79" t="n">
-        <v>0.06820890186166248</v>
+        <v>0.08919625628063554</v>
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="2" t="n">
+      <c r="A80" s="3" t="n">
         <v>51502</v>
       </c>
       <c r="B80" t="n">
@@ -3391,29 +3392,29 @@
         <v>0.08</v>
       </c>
       <c r="E80" t="n">
-        <v>0.4599029927197631</v>
+        <v>0.1089050369639545</v>
       </c>
       <c r="F80" t="n">
         <v>0</v>
       </c>
       <c r="G80" t="n">
-        <v>0.4599029927197631</v>
+        <v>0.6014116058643056</v>
       </c>
       <c r="H80" t="n">
         <v>0</v>
       </c>
       <c r="I80" t="n">
-        <v>0.08328032238420052</v>
+        <v>0.6014116058643056</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
       </c>
       <c r="K80" t="n">
-        <v>0.08328032238420052</v>
+        <v>0.1089050369639545</v>
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="2" t="n">
+      <c r="A81" s="3" t="n">
         <v>53328</v>
       </c>
       <c r="B81" t="n">
@@ -3428,29 +3429,29 @@
         <v>0.08</v>
       </c>
       <c r="E81" t="n">
-        <v>0.4599029927197631</v>
+        <v>0.1257467230135668</v>
       </c>
       <c r="F81" t="n">
         <v>0</v>
       </c>
       <c r="G81" t="n">
-        <v>0.4599029927197631</v>
+        <v>0.6014116058643056</v>
       </c>
       <c r="H81" t="n">
         <v>0</v>
       </c>
       <c r="I81" t="n">
-        <v>0.09615925877508052</v>
+        <v>0.6014116058643056</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
       </c>
       <c r="K81" t="n">
-        <v>0.09615925877508052</v>
+        <v>0.1257467230135668</v>
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="2" t="n">
+      <c r="A82" s="3" t="n">
         <v>46023</v>
       </c>
       <c r="B82" t="n">
@@ -3463,7 +3464,7 @@
       </c>
       <c r="D82" t="inlineStr"/>
       <c r="E82" t="n">
-        <v>1</v>
+        <v>0.2712070570783821</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>
@@ -3475,7 +3476,7 @@
         <v>0</v>
       </c>
       <c r="I82" t="n">
-        <v>0.2712070570783821</v>
+        <v>1</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -3485,7 +3486,7 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="2" t="n">
+      <c r="A83" s="3" t="n">
         <v>47849</v>
       </c>
       <c r="B83" t="n">
@@ -3498,7 +3499,7 @@
       </c>
       <c r="D83" t="inlineStr"/>
       <c r="E83" t="n">
-        <v>1</v>
+        <v>0.4370978189737727</v>
       </c>
       <c r="F83" t="n">
         <v>0</v>
@@ -3510,7 +3511,7 @@
         <v>0</v>
       </c>
       <c r="I83" t="n">
-        <v>0.4370978189737727</v>
+        <v>1</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -3520,7 +3521,7 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="2" t="n">
+      <c r="A84" s="3" t="n">
         <v>49675</v>
       </c>
       <c r="B84" t="n">
@@ -3533,7 +3534,7 @@
       </c>
       <c r="D84" t="inlineStr"/>
       <c r="E84" t="n">
-        <v>1</v>
+        <v>0.5456964388783678</v>
       </c>
       <c r="F84" t="n">
         <v>0</v>
@@ -3545,7 +3546,7 @@
         <v>0</v>
       </c>
       <c r="I84" t="n">
-        <v>0.5456964388783678</v>
+        <v>1</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -3555,7 +3556,7 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="2" t="n">
+      <c r="A85" s="3" t="n">
         <v>51502</v>
       </c>
       <c r="B85" t="n">
@@ -3568,7 +3569,7 @@
       </c>
       <c r="D85" t="inlineStr"/>
       <c r="E85" t="n">
-        <v>1</v>
+        <v>0.6207578627767205</v>
       </c>
       <c r="F85" t="n">
         <v>0</v>
@@ -3580,7 +3581,7 @@
         <v>0</v>
       </c>
       <c r="I85" t="n">
-        <v>0.6207578627767205</v>
+        <v>1</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -3590,7 +3591,7 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="2" t="n">
+      <c r="A86" s="3" t="n">
         <v>53328</v>
       </c>
       <c r="B86" t="n">
@@ -3603,7 +3604,7 @@
       </c>
       <c r="D86" t="inlineStr"/>
       <c r="E86" t="n">
-        <v>1</v>
+        <v>0.6749874416447547</v>
       </c>
       <c r="F86" t="n">
         <v>0</v>
@@ -3615,7 +3616,7 @@
         <v>0</v>
       </c>
       <c r="I86" t="n">
-        <v>0.6749874416447547</v>
+        <v>1</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -3625,7 +3626,7 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="2" t="n">
+      <c r="A87" s="3" t="n">
         <v>46023</v>
       </c>
       <c r="B87" t="n">
@@ -3638,7 +3639,7 @@
       </c>
       <c r="D87" t="inlineStr"/>
       <c r="E87" t="n">
-        <v>1</v>
+        <v>0.2712070570783821</v>
       </c>
       <c r="F87" t="n">
         <v>0</v>
@@ -3650,7 +3651,7 @@
         <v>0</v>
       </c>
       <c r="I87" t="n">
-        <v>0.2712070570783821</v>
+        <v>1</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -3660,7 +3661,7 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="2" t="n">
+      <c r="A88" s="3" t="n">
         <v>47849</v>
       </c>
       <c r="B88" t="n">
@@ -3673,7 +3674,7 @@
       </c>
       <c r="D88" t="inlineStr"/>
       <c r="E88" t="n">
-        <v>1</v>
+        <v>0.4370978189737727</v>
       </c>
       <c r="F88" t="n">
         <v>0</v>
@@ -3685,7 +3686,7 @@
         <v>0</v>
       </c>
       <c r="I88" t="n">
-        <v>0.4370978189737727</v>
+        <v>1</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -3695,7 +3696,7 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="2" t="n">
+      <c r="A89" s="3" t="n">
         <v>49675</v>
       </c>
       <c r="B89" t="n">
@@ -3708,7 +3709,7 @@
       </c>
       <c r="D89" t="inlineStr"/>
       <c r="E89" t="n">
-        <v>1</v>
+        <v>0.5456964388783678</v>
       </c>
       <c r="F89" t="n">
         <v>0</v>
@@ -3720,7 +3721,7 @@
         <v>0</v>
       </c>
       <c r="I89" t="n">
-        <v>0.5456964388783678</v>
+        <v>1</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -3730,7 +3731,7 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="2" t="n">
+      <c r="A90" s="3" t="n">
         <v>51502</v>
       </c>
       <c r="B90" t="n">
@@ -3743,7 +3744,7 @@
       </c>
       <c r="D90" t="inlineStr"/>
       <c r="E90" t="n">
-        <v>1</v>
+        <v>0.6207578627767205</v>
       </c>
       <c r="F90" t="n">
         <v>0</v>
@@ -3755,7 +3756,7 @@
         <v>0</v>
       </c>
       <c r="I90" t="n">
-        <v>0.6207578627767205</v>
+        <v>1</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -3765,7 +3766,7 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="2" t="n">
+      <c r="A91" s="3" t="n">
         <v>53328</v>
       </c>
       <c r="B91" t="n">
@@ -3778,7 +3779,7 @@
       </c>
       <c r="D91" t="inlineStr"/>
       <c r="E91" t="n">
-        <v>1</v>
+        <v>0.6749874416447547</v>
       </c>
       <c r="F91" t="n">
         <v>0</v>
@@ -3790,7 +3791,7 @@
         <v>0</v>
       </c>
       <c r="I91" t="n">
-        <v>0.6749874416447547</v>
+        <v>1</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -3800,7 +3801,7 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="2" t="n">
+      <c r="A92" s="3" t="n">
         <v>46023</v>
       </c>
       <c r="B92" t="n">
@@ -3813,7 +3814,7 @@
       </c>
       <c r="D92" t="inlineStr"/>
       <c r="E92" t="n">
-        <v>1</v>
+        <v>0.2712070570783821</v>
       </c>
       <c r="F92" t="n">
         <v>0</v>
@@ -3825,7 +3826,7 @@
         <v>0</v>
       </c>
       <c r="I92" t="n">
-        <v>0.2712070570783821</v>
+        <v>1</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -3835,7 +3836,7 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="2" t="n">
+      <c r="A93" s="3" t="n">
         <v>47849</v>
       </c>
       <c r="B93" t="n">
@@ -3848,7 +3849,7 @@
       </c>
       <c r="D93" t="inlineStr"/>
       <c r="E93" t="n">
-        <v>1</v>
+        <v>0.4370978189737727</v>
       </c>
       <c r="F93" t="n">
         <v>0</v>
@@ -3860,7 +3861,7 @@
         <v>0</v>
       </c>
       <c r="I93" t="n">
-        <v>0.4370978189737727</v>
+        <v>1</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -3870,7 +3871,7 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="2" t="n">
+      <c r="A94" s="3" t="n">
         <v>49675</v>
       </c>
       <c r="B94" t="n">
@@ -3883,7 +3884,7 @@
       </c>
       <c r="D94" t="inlineStr"/>
       <c r="E94" t="n">
-        <v>1</v>
+        <v>0.5456964388783678</v>
       </c>
       <c r="F94" t="n">
         <v>0</v>
@@ -3895,7 +3896,7 @@
         <v>0</v>
       </c>
       <c r="I94" t="n">
-        <v>0.5456964388783678</v>
+        <v>1</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -3905,7 +3906,7 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="2" t="n">
+      <c r="A95" s="3" t="n">
         <v>51502</v>
       </c>
       <c r="B95" t="n">
@@ -3918,7 +3919,7 @@
       </c>
       <c r="D95" t="inlineStr"/>
       <c r="E95" t="n">
-        <v>1</v>
+        <v>0.6207578627767205</v>
       </c>
       <c r="F95" t="n">
         <v>0</v>
@@ -3930,7 +3931,7 @@
         <v>0</v>
       </c>
       <c r="I95" t="n">
-        <v>0.6207578627767205</v>
+        <v>1</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -3940,7 +3941,7 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="2" t="n">
+      <c r="A96" s="3" t="n">
         <v>53328</v>
       </c>
       <c r="B96" t="n">
@@ -3953,7 +3954,7 @@
       </c>
       <c r="D96" t="inlineStr"/>
       <c r="E96" t="n">
-        <v>1</v>
+        <v>0.6749874416447547</v>
       </c>
       <c r="F96" t="n">
         <v>0</v>
@@ -3965,7 +3966,7 @@
         <v>0</v>
       </c>
       <c r="I96" t="n">
-        <v>0.6749874416447547</v>
+        <v>1</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>

--- a/data/Arisdorf/investment_decision/Arisdorf_MFH_2005-2014_investment_decision.xlsx
+++ b/data/Arisdorf/investment_decision/Arisdorf_MFH_2005-2014_investment_decision.xlsx
@@ -441,52 +441,52 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>scen_base_invested_available_unit</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>scale_MW</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>scen_base_candidate_unit</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>scen_cp_dr_invested_available_unit</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>scen_cp_dr_candidate_unit</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>scen_cp_cu_invested_available_unit</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>scen_cp_cu_candidate_unit</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
           <t>scen_all_invested_available_unit</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>scale_MW</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>scen_all_candidate_unit</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>scen_base_invested_available_unit</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>scen_base_candidate_unit</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>scen_cp_dr_invested_available_unit</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>scen_cp_dr_candidate_unit</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>scen_cp_cu_invested_available_unit</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>scen_cp_cu_candidate_unit</t>
         </is>
       </c>
     </row>
@@ -495,7 +495,7 @@
         <v>46023</v>
       </c>
       <c r="B2" t="n">
-        <v>5.182471626152436</v>
+        <v>2.30023070629705</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -509,19 +509,19 @@
         <v>1500.192929592385</v>
       </c>
       <c r="F2" t="n">
-        <v>5.221614923124662</v>
+        <v>2.332311367070473</v>
       </c>
       <c r="G2" t="n">
         <v>1500.192929592385</v>
       </c>
       <c r="H2" t="n">
-        <v>5.182471626152437</v>
+        <v>2.296232928424813</v>
       </c>
       <c r="I2" t="n">
         <v>1500.192929592385</v>
       </c>
       <c r="J2" t="n">
-        <v>5.228096530781166</v>
+        <v>2.35965102321558</v>
       </c>
       <c r="K2" t="n">
         <v>1500.192929592385</v>
@@ -532,7 +532,7 @@
         <v>47849</v>
       </c>
       <c r="B3" t="n">
-        <v>8.570364869034156</v>
+        <v>2.77431455162031</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -546,19 +546,19 @@
         <v>1500.192929592385</v>
       </c>
       <c r="F3" t="n">
-        <v>7.578689065828083</v>
+        <v>2.774314551620324</v>
       </c>
       <c r="G3" t="n">
         <v>1500.192929592385</v>
       </c>
       <c r="H3" t="n">
-        <v>7.585505056345466</v>
+        <v>2.86755612186674</v>
       </c>
       <c r="I3" t="n">
         <v>1500.192929592385</v>
       </c>
       <c r="J3" t="n">
-        <v>8.570364869034156</v>
+        <v>2.868830011102558</v>
       </c>
       <c r="K3" t="n">
         <v>1500.192929592385</v>
@@ -569,7 +569,7 @@
         <v>49675</v>
       </c>
       <c r="B4" t="n">
-        <v>8.570364869034156</v>
+        <v>2.77431455162031</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -583,19 +583,19 @@
         <v>1500.192929592385</v>
       </c>
       <c r="F4" t="n">
-        <v>7.578689065828083</v>
+        <v>2.774314551620325</v>
       </c>
       <c r="G4" t="n">
         <v>1500.192929592385</v>
       </c>
       <c r="H4" t="n">
-        <v>7.585505056345467</v>
+        <v>2.86755612186674</v>
       </c>
       <c r="I4" t="n">
         <v>1500.192929592385</v>
       </c>
       <c r="J4" t="n">
-        <v>8.570364869034156</v>
+        <v>2.868830011102558</v>
       </c>
       <c r="K4" t="n">
         <v>1500.192929592385</v>
@@ -606,7 +606,7 @@
         <v>51502</v>
       </c>
       <c r="B5" t="n">
-        <v>8.570364869034156</v>
+        <v>2.77431455162031</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -620,19 +620,19 @@
         <v>1500.192929592385</v>
       </c>
       <c r="F5" t="n">
-        <v>7.810995102943164</v>
+        <v>2.779136168091029</v>
       </c>
       <c r="G5" t="n">
         <v>1500.192929592385</v>
       </c>
       <c r="H5" t="n">
-        <v>7.783120634920661</v>
+        <v>2.86755612186674</v>
       </c>
       <c r="I5" t="n">
         <v>1500.192929592385</v>
       </c>
       <c r="J5" t="n">
-        <v>8.570364869034156</v>
+        <v>2.868830011102558</v>
       </c>
       <c r="K5" t="n">
         <v>1500.192929592385</v>
@@ -643,7 +643,7 @@
         <v>53328</v>
       </c>
       <c r="B6" t="n">
-        <v>8.570364869034156</v>
+        <v>2.77431455162031</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -657,19 +657,19 @@
         <v>1500.192929592385</v>
       </c>
       <c r="F6" t="n">
-        <v>7.810995102943164</v>
+        <v>2.779136168091029</v>
       </c>
       <c r="G6" t="n">
         <v>1500.192929592385</v>
       </c>
       <c r="H6" t="n">
-        <v>7.783120634920661</v>
+        <v>2.86755612186674</v>
       </c>
       <c r="I6" t="n">
         <v>1500.192929592385</v>
       </c>
       <c r="J6" t="n">
-        <v>8.570364869034156</v>
+        <v>2.868830011102558</v>
       </c>
       <c r="K6" t="n">
         <v>1500.192929592385</v>
@@ -684,32 +684,32 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>BLVL_VanadiumRedox_s_2 MWh_d_Arisdorf_b_MFH_2005-2014</t>
+          <t>BLVL_Li-ion_s_3 MWh_d_Arisdorf_b_MFH_2005-2014</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>2</v>
+        <v>0.0125</v>
       </c>
       <c r="E7" t="n">
-        <v>1.083577073379877</v>
+        <v>0.01986562499999999</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>2.250289394388578</v>
+        <v>0.01986562499999999</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>2.250289394388578</v>
+        <v>0.009565852219736775</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>1.083577073379877</v>
+        <v>0.009565852219736775</v>
       </c>
     </row>
     <row r="8">
@@ -721,32 +721,32 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>BLVL_VanadiumRedox_s_2 MWh_d_Arisdorf_b_MFH_2005-2014</t>
+          <t>BLVL_Li-ion_s_3 MWh_d_Arisdorf_b_MFH_2005-2014</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>2</v>
+        <v>0.0125</v>
       </c>
       <c r="E8" t="n">
-        <v>1.543327622275662</v>
+        <v>0.01986562499999999</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>2.250289394388578</v>
+        <v>0.01986562499999999</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>2.250289394388578</v>
+        <v>0.01362454441314215</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>1.543327622275662</v>
+        <v>0.01362454441314215</v>
       </c>
     </row>
     <row r="9">
@@ -758,32 +758,32 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>BLVL_VanadiumRedox_s_2 MWh_d_Arisdorf_b_MFH_2005-2014</t>
+          <t>BLVL_Li-ion_s_3 MWh_d_Arisdorf_b_MFH_2005-2014</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>2</v>
+        <v>0.0125</v>
       </c>
       <c r="E9" t="n">
-        <v>1.774716894167666</v>
+        <v>0.01986562499999999</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>2.250289394388578</v>
+        <v>0.01986562499999999</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>2.250289394388578</v>
+        <v>0.01566725612652982</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>1.774716894167666</v>
+        <v>0.01566725612652982</v>
       </c>
     </row>
     <row r="10">
@@ -795,32 +795,32 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>BLVL_VanadiumRedox_s_2 MWh_d_Arisdorf_b_MFH_2005-2014</t>
+          <t>BLVL_Li-ion_s_3 MWh_d_Arisdorf_b_MFH_2005-2014</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>2</v>
+        <v>0.0125</v>
       </c>
       <c r="E10" t="n">
-        <v>1.905727440522057</v>
+        <v>0.01986562499999999</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>2.250289394388578</v>
+        <v>0.01986562499999999</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>2.250289394388578</v>
+        <v>0.01682382131828312</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>1.905727440522057</v>
+        <v>0.01682382131828312</v>
       </c>
     </row>
     <row r="11">
@@ -832,32 +832,32 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>BLVL_VanadiumRedox_s_2 MWh_d_Arisdorf_b_MFH_2005-2014</t>
+          <t>BLVL_Li-ion_s_3 MWh_d_Arisdorf_b_MFH_2005-2014</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>2</v>
+        <v>0.0125</v>
       </c>
       <c r="E11" t="n">
-        <v>1.986587163207542</v>
+        <v>0.01986562499999999</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>2.250289394388578</v>
+        <v>0.01986562499999999</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>2.250289394388578</v>
+        <v>0.01753765347359588</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>1.986587163207542</v>
+        <v>0.01753765347359588</v>
       </c>
     </row>
     <row r="12">
@@ -865,7 +865,7 @@
         <v>46023</v>
       </c>
       <c r="B12" t="n">
-        <v>0.0008306878870588232</v>
+        <v>0.0006922399058823529</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -879,19 +879,19 @@
         <v>1</v>
       </c>
       <c r="F12" t="n">
-        <v>0.0008306878870588232</v>
+        <v>0.0006922399058823437</v>
       </c>
       <c r="G12" t="n">
         <v>1</v>
       </c>
       <c r="H12" t="n">
-        <v>0.0008306878870588232</v>
+        <v>0.0006574146327925939</v>
       </c>
       <c r="I12" t="n">
         <v>1</v>
       </c>
       <c r="J12" t="n">
-        <v>0.0008306878870588232</v>
+        <v>0.0006570252115574261</v>
       </c>
       <c r="K12" t="n">
         <v>1</v>
@@ -902,7 +902,7 @@
         <v>47849</v>
       </c>
       <c r="B13" t="n">
-        <v>0.0008306878870588232</v>
+        <v>0.0006922399058823529</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -916,19 +916,19 @@
         <v>1</v>
       </c>
       <c r="F13" t="n">
-        <v>0.0008306878870588232</v>
+        <v>0.0006922399058823437</v>
       </c>
       <c r="G13" t="n">
         <v>1</v>
       </c>
       <c r="H13" t="n">
-        <v>0.0008306878870588232</v>
+        <v>0.0006574146327925939</v>
       </c>
       <c r="I13" t="n">
         <v>1</v>
       </c>
       <c r="J13" t="n">
-        <v>0.0008306878870588232</v>
+        <v>0.0006570252115574261</v>
       </c>
       <c r="K13" t="n">
         <v>1</v>
@@ -939,7 +939,7 @@
         <v>49675</v>
       </c>
       <c r="B14" t="n">
-        <v>0.0008306878870588232</v>
+        <v>0.0006922399058823529</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -953,19 +953,19 @@
         <v>1</v>
       </c>
       <c r="F14" t="n">
-        <v>0.0008306878870588232</v>
+        <v>0.0006922399058823437</v>
       </c>
       <c r="G14" t="n">
         <v>1</v>
       </c>
       <c r="H14" t="n">
-        <v>0.0008306878870588232</v>
+        <v>0.0006574146327925939</v>
       </c>
       <c r="I14" t="n">
         <v>1</v>
       </c>
       <c r="J14" t="n">
-        <v>0.0008306878870588232</v>
+        <v>0.0006570252115574261</v>
       </c>
       <c r="K14" t="n">
         <v>1</v>
@@ -976,7 +976,7 @@
         <v>51502</v>
       </c>
       <c r="B15" t="n">
-        <v>0.0008306878870588232</v>
+        <v>0.0007788514642789299</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -990,19 +990,19 @@
         <v>1</v>
       </c>
       <c r="F15" t="n">
-        <v>0.0008306878870588232</v>
+        <v>0.000796075891764706</v>
       </c>
       <c r="G15" t="n">
         <v>1</v>
       </c>
       <c r="H15" t="n">
-        <v>0.0008306878870588232</v>
+        <v>0.0006574146327925938</v>
       </c>
       <c r="I15" t="n">
         <v>1</v>
       </c>
       <c r="J15" t="n">
-        <v>0.0008306878870588232</v>
+        <v>0.0006570252115574261</v>
       </c>
       <c r="K15" t="n">
         <v>1</v>
@@ -1013,7 +1013,7 @@
         <v>53328</v>
       </c>
       <c r="B16" t="n">
-        <v>0.0008306878870588232</v>
+        <v>0.0007788514642789299</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -1027,19 +1027,19 @@
         <v>1</v>
       </c>
       <c r="F16" t="n">
-        <v>0.0008306878870588232</v>
+        <v>0.000796075891764706</v>
       </c>
       <c r="G16" t="n">
         <v>1</v>
       </c>
       <c r="H16" t="n">
-        <v>0.0008306878870588232</v>
+        <v>0.0006574146327925939</v>
       </c>
       <c r="I16" t="n">
         <v>1</v>
       </c>
       <c r="J16" t="n">
-        <v>0.0008306878870588232</v>
+        <v>0.0006570252115574261</v>
       </c>
       <c r="K16" t="n">
         <v>1</v>
@@ -1050,7 +1050,7 @@
         <v>46023</v>
       </c>
       <c r="B17" t="n">
-        <v>0.05464918343696924</v>
+        <v>0.04372641467501462</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -1064,19 +1064,19 @@
         <v>0.1235648232</v>
       </c>
       <c r="F17" t="n">
-        <v>0.05464918343696901</v>
+        <v>0.0439454948466237</v>
       </c>
       <c r="G17" t="n">
         <v>0.1235648232</v>
       </c>
       <c r="H17" t="n">
-        <v>0.05464918343696901</v>
+        <v>0.03887414718686945</v>
       </c>
       <c r="I17" t="n">
         <v>0.1235648232</v>
       </c>
       <c r="J17" t="n">
-        <v>0.05464918343696924</v>
+        <v>0.03887414718686946</v>
       </c>
       <c r="K17" t="n">
         <v>0.1235648232</v>
@@ -1087,7 +1087,7 @@
         <v>47849</v>
       </c>
       <c r="B18" t="n">
-        <v>0.05464918343696924</v>
+        <v>0.04372641467501462</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -1101,19 +1101,19 @@
         <v>0.1235648232</v>
       </c>
       <c r="F18" t="n">
-        <v>0.05464918343696901</v>
+        <v>0.0439454948466237</v>
       </c>
       <c r="G18" t="n">
         <v>0.1235648232</v>
       </c>
       <c r="H18" t="n">
-        <v>0.05464918343696901</v>
+        <v>0.03887414718686945</v>
       </c>
       <c r="I18" t="n">
         <v>0.1235648232</v>
       </c>
       <c r="J18" t="n">
-        <v>0.05464918343696924</v>
+        <v>0.03887414718686946</v>
       </c>
       <c r="K18" t="n">
         <v>0.1235648232</v>
@@ -1124,7 +1124,7 @@
         <v>49675</v>
       </c>
       <c r="B19" t="n">
-        <v>0.05464918343696924</v>
+        <v>0.04372641467501462</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -1138,19 +1138,19 @@
         <v>0.1235648232</v>
       </c>
       <c r="F19" t="n">
-        <v>0.05464918343696901</v>
+        <v>0.0439454948466237</v>
       </c>
       <c r="G19" t="n">
         <v>0.1235648232</v>
       </c>
       <c r="H19" t="n">
-        <v>0.05464918343696901</v>
+        <v>0.03887414718686945</v>
       </c>
       <c r="I19" t="n">
         <v>0.1235648232</v>
       </c>
       <c r="J19" t="n">
-        <v>0.05464918343696924</v>
+        <v>0.03887414718686946</v>
       </c>
       <c r="K19" t="n">
         <v>0.1235648232</v>
@@ -1161,7 +1161,7 @@
         <v>51502</v>
       </c>
       <c r="B20" t="n">
-        <v>0.02377320155791523</v>
+        <v>0.03750848507426698</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -1175,19 +1175,19 @@
         <v>0.1235648232</v>
       </c>
       <c r="F20" t="n">
-        <v>0.02377320155791523</v>
+        <v>0.04061498910385838</v>
       </c>
       <c r="G20" t="n">
         <v>0.1235648232</v>
       </c>
       <c r="H20" t="n">
-        <v>0.02377320155791523</v>
+        <v>0.02305167498590968</v>
       </c>
       <c r="I20" t="n">
         <v>0.1235648232</v>
       </c>
       <c r="J20" t="n">
-        <v>0.02377320155791523</v>
+        <v>0.02308001615416481</v>
       </c>
       <c r="K20" t="n">
         <v>0.1235648232</v>
@@ -1198,7 +1198,7 @@
         <v>53328</v>
       </c>
       <c r="B21" t="n">
-        <v>0.02377320155791523</v>
+        <v>0.03750848507426698</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -1212,19 +1212,19 @@
         <v>0.1235648232</v>
       </c>
       <c r="F21" t="n">
-        <v>0.02377320155791523</v>
+        <v>0.0408134803142639</v>
       </c>
       <c r="G21" t="n">
         <v>0.1235648232</v>
       </c>
       <c r="H21" t="n">
-        <v>0.02377320155791523</v>
+        <v>0.02368404539344653</v>
       </c>
       <c r="I21" t="n">
         <v>0.1235648232</v>
       </c>
       <c r="J21" t="n">
-        <v>0.02377320155791523</v>
+        <v>0.02368508518279567</v>
       </c>
       <c r="K21" t="n">
         <v>0.1235648232</v>
@@ -1420,7 +1420,7 @@
         <v>46023</v>
       </c>
       <c r="B27" t="n">
-        <v>0</v>
+        <v>0.01281242651715367</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -1434,19 +1434,19 @@
         <v>0.1235648232</v>
       </c>
       <c r="F27" t="n">
-        <v>0</v>
+        <v>0.01259334634554466</v>
       </c>
       <c r="G27" t="n">
         <v>0.1235648232</v>
       </c>
       <c r="H27" t="n">
-        <v>0</v>
+        <v>0.01766469400529885</v>
       </c>
       <c r="I27" t="n">
         <v>0.1235648232</v>
       </c>
       <c r="J27" t="n">
-        <v>0</v>
+        <v>0.01766469400529885</v>
       </c>
       <c r="K27" t="n">
         <v>0.1235648232</v>
@@ -1457,7 +1457,7 @@
         <v>47849</v>
       </c>
       <c r="B28" t="n">
-        <v>0</v>
+        <v>0.01281242651715367</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -1471,19 +1471,19 @@
         <v>0.1235648232</v>
       </c>
       <c r="F28" t="n">
-        <v>0</v>
+        <v>0.01338298138036717</v>
       </c>
       <c r="G28" t="n">
         <v>0.1235648232</v>
       </c>
       <c r="H28" t="n">
-        <v>0</v>
+        <v>0.01841028326578687</v>
       </c>
       <c r="I28" t="n">
         <v>0.1235648232</v>
       </c>
       <c r="J28" t="n">
-        <v>0</v>
+        <v>0.01838303218346514</v>
       </c>
       <c r="K28" t="n">
         <v>0.1235648232</v>
@@ -1494,7 +1494,7 @@
         <v>49675</v>
       </c>
       <c r="B29" t="n">
-        <v>0</v>
+        <v>0.0179573628950194</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -1508,19 +1508,19 @@
         <v>0.1235648232</v>
       </c>
       <c r="F29" t="n">
-        <v>0</v>
+        <v>0.01769560158119902</v>
       </c>
       <c r="G29" t="n">
         <v>0.1235648232</v>
       </c>
       <c r="H29" t="n">
-        <v>0</v>
+        <v>0.0314260310675888</v>
       </c>
       <c r="I29" t="n">
         <v>0.1235648232</v>
       </c>
       <c r="J29" t="n">
-        <v>0</v>
+        <v>0.0315071240356046</v>
       </c>
       <c r="K29" t="n">
         <v>0.1235648232</v>
@@ -1531,7 +1531,7 @@
         <v>51502</v>
       </c>
       <c r="B30" t="n">
-        <v>0</v>
+        <v>0.01654019342036369</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -1545,19 +1545,19 @@
         <v>0.1235648232</v>
       </c>
       <c r="F30" t="n">
-        <v>0</v>
+        <v>0.01384826343139827</v>
       </c>
       <c r="G30" t="n">
         <v>0.1235648232</v>
       </c>
       <c r="H30" t="n">
-        <v>0</v>
+        <v>0.03023752337778753</v>
       </c>
       <c r="I30" t="n">
         <v>0.1235648232</v>
       </c>
       <c r="J30" t="n">
-        <v>0</v>
+        <v>0.03020257095018977</v>
       </c>
       <c r="K30" t="n">
         <v>0.1235648232</v>
@@ -1568,7 +1568,7 @@
         <v>53328</v>
       </c>
       <c r="B31" t="n">
-        <v>0</v>
+        <v>0.01654019342036369</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -1582,19 +1582,19 @@
         <v>0.1235648232</v>
       </c>
       <c r="F31" t="n">
-        <v>0</v>
+        <v>0.0130586283965758</v>
       </c>
       <c r="G31" t="n">
         <v>0.1235648232</v>
       </c>
       <c r="H31" t="n">
-        <v>0</v>
+        <v>0.0294919341172995</v>
       </c>
       <c r="I31" t="n">
         <v>0.1235648232</v>
       </c>
       <c r="J31" t="n">
-        <v>0</v>
+        <v>0.02948423277202348</v>
       </c>
       <c r="K31" t="n">
         <v>0.1235648232</v>
@@ -1986,7 +1986,7 @@
         <v>0.03</v>
       </c>
       <c r="E42" t="n">
-        <v>0.2046115363271334</v>
+        <v>0.402678944077692</v>
       </c>
       <c r="F42" t="n">
         <v>0</v>
@@ -1998,7 +1998,7 @@
         <v>0</v>
       </c>
       <c r="I42" t="n">
-        <v>0.402678944077692</v>
+        <v>0.2046115363271334</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -2023,7 +2023,7 @@
         <v>0.03</v>
       </c>
       <c r="E43" t="n">
-        <v>0.2871971342961154</v>
+        <v>0.402678944077692</v>
       </c>
       <c r="F43" t="n">
         <v>0</v>
@@ -2035,7 +2035,7 @@
         <v>0</v>
       </c>
       <c r="I43" t="n">
-        <v>0.402678944077692</v>
+        <v>0.2871971342961154</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -2060,7 +2060,7 @@
         <v>0.03</v>
       </c>
       <c r="E44" t="n">
-        <v>0.3272143951258143</v>
+        <v>0.402678944077692</v>
       </c>
       <c r="F44" t="n">
         <v>0</v>
@@ -2072,7 +2072,7 @@
         <v>0</v>
       </c>
       <c r="I44" t="n">
-        <v>0.402678944077692</v>
+        <v>0.3272143951258143</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -2097,7 +2097,7 @@
         <v>0.03</v>
       </c>
       <c r="E45" t="n">
-        <v>0.3492170049785441</v>
+        <v>0.402678944077692</v>
       </c>
       <c r="F45" t="n">
         <v>0</v>
@@ -2109,7 +2109,7 @@
         <v>0</v>
       </c>
       <c r="I45" t="n">
-        <v>0.402678944077692</v>
+        <v>0.3492170049785441</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -2123,7 +2123,7 @@
         <v>53328</v>
       </c>
       <c r="B46" t="n">
-        <v>0.3667758145154252</v>
+        <v>0</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -2134,7 +2134,7 @@
         <v>0.03</v>
       </c>
       <c r="E46" t="n">
-        <v>0.3624849667870516</v>
+        <v>0.402678944077692</v>
       </c>
       <c r="F46" t="n">
         <v>0</v>
@@ -2146,10 +2146,10 @@
         <v>0</v>
       </c>
       <c r="I46" t="n">
-        <v>0.402678944077692</v>
+        <v>0.3624849667870516</v>
       </c>
       <c r="J46" t="n">
-        <v>0</v>
+        <v>0.3667758145154252</v>
       </c>
       <c r="K46" t="n">
         <v>0.3624849667870516</v>
@@ -2345,7 +2345,7 @@
         <v>46023</v>
       </c>
       <c r="B52" t="n">
-        <v>0.0841929480131922</v>
+        <v>0.08324832969047238</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -2356,22 +2356,22 @@
         <v>0.08</v>
       </c>
       <c r="E52" t="n">
+        <v>0.6014116058643056</v>
+      </c>
+      <c r="F52" t="n">
+        <v>0.08611533981310647</v>
+      </c>
+      <c r="G52" t="n">
+        <v>0.6014116058643056</v>
+      </c>
+      <c r="H52" t="n">
+        <v>0.07702413761473004</v>
+      </c>
+      <c r="I52" t="n">
         <v>0.1323240299819102</v>
       </c>
-      <c r="F52" t="n">
-        <v>0.08502985723903585</v>
-      </c>
-      <c r="G52" t="n">
-        <v>0.6014116058643056</v>
-      </c>
-      <c r="H52" t="n">
-        <v>0.0841929480131922</v>
-      </c>
-      <c r="I52" t="n">
-        <v>0.6014116058643056</v>
-      </c>
       <c r="J52" t="n">
-        <v>0.08394654034242725</v>
+        <v>0.08629898926991136</v>
       </c>
       <c r="K52" t="n">
         <v>0.1323240299819102</v>
@@ -2382,7 +2382,7 @@
         <v>47849</v>
       </c>
       <c r="B53" t="n">
-        <v>0.08821042176137427</v>
+        <v>0.08787047251319219</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -2393,22 +2393,22 @@
         <v>0.08</v>
       </c>
       <c r="E53" t="n">
+        <v>0.6014116058643056</v>
+      </c>
+      <c r="F53" t="n">
+        <v>0.09067676803252166</v>
+      </c>
+      <c r="G53" t="n">
+        <v>0.6014116058643056</v>
+      </c>
+      <c r="H53" t="n">
+        <v>0.08187178724319484</v>
+      </c>
+      <c r="I53" t="n">
         <v>0.2154936369329378</v>
       </c>
-      <c r="F53" t="n">
-        <v>0.08973961729908206</v>
-      </c>
-      <c r="G53" t="n">
-        <v>0.6014116058643056</v>
-      </c>
-      <c r="H53" t="n">
-        <v>0.08972557654522417</v>
-      </c>
-      <c r="I53" t="n">
-        <v>0.6014116058643056</v>
-      </c>
       <c r="J53" t="n">
-        <v>0.0878704725131922</v>
+        <v>0.08951979137438333</v>
       </c>
       <c r="K53" t="n">
         <v>0.2154936369329378</v>
@@ -2419,7 +2419,7 @@
         <v>49675</v>
       </c>
       <c r="B54" t="n">
-        <v>0.08821042176137427</v>
+        <v>0.0878704725131922</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -2430,22 +2430,22 @@
         <v>0.08</v>
       </c>
       <c r="E54" t="n">
+        <v>0.6014116058643056</v>
+      </c>
+      <c r="F54" t="n">
+        <v>0.09067676803252166</v>
+      </c>
+      <c r="G54" t="n">
+        <v>0.6014116058643056</v>
+      </c>
+      <c r="H54" t="n">
+        <v>0.08187178724319484</v>
+      </c>
+      <c r="I54" t="n">
         <v>0.2711964643509661</v>
       </c>
-      <c r="F54" t="n">
-        <v>0.08973961729908206</v>
-      </c>
-      <c r="G54" t="n">
-        <v>0.6014116058643056</v>
-      </c>
-      <c r="H54" t="n">
-        <v>0.08972557654522417</v>
-      </c>
-      <c r="I54" t="n">
-        <v>0.6014116058643056</v>
-      </c>
       <c r="J54" t="n">
-        <v>0.0878704725131922</v>
+        <v>0.08951979137438333</v>
       </c>
       <c r="K54" t="n">
         <v>0.2711964643509661</v>
@@ -2456,7 +2456,7 @@
         <v>51502</v>
       </c>
       <c r="B55" t="n">
-        <v>0.08114859928711876</v>
+        <v>0.08787047251319219</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -2467,22 +2467,22 @@
         <v>0.08</v>
       </c>
       <c r="E55" t="n">
+        <v>0.6014116058643056</v>
+      </c>
+      <c r="F55" t="n">
+        <v>0.08290197902662017</v>
+      </c>
+      <c r="G55" t="n">
+        <v>0.6014116058643056</v>
+      </c>
+      <c r="H55" t="n">
+        <v>0.08263596168571394</v>
+      </c>
+      <c r="I55" t="n">
         <v>0.3104699533606</v>
       </c>
-      <c r="F55" t="n">
-        <v>0.0823541857631922</v>
-      </c>
-      <c r="G55" t="n">
-        <v>0.6014116058643056</v>
-      </c>
-      <c r="H55" t="n">
-        <v>0.08114859928711876</v>
-      </c>
-      <c r="I55" t="n">
-        <v>0.6014116058643056</v>
-      </c>
       <c r="J55" t="n">
-        <v>0.08229131555511543</v>
+        <v>0.08263093626768865</v>
       </c>
       <c r="K55" t="n">
         <v>0.3104699533606</v>
@@ -2493,7 +2493,7 @@
         <v>53328</v>
       </c>
       <c r="B56" t="n">
-        <v>0.08543131419974906</v>
+        <v>0.09010704709566664</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -2504,22 +2504,22 @@
         <v>0.08</v>
       </c>
       <c r="E56" t="n">
+        <v>0.6014116058643056</v>
+      </c>
+      <c r="F56" t="n">
+        <v>0.08999672077815801</v>
+      </c>
+      <c r="G56" t="n">
+        <v>0.6014116058643056</v>
+      </c>
+      <c r="H56" t="n">
+        <v>0.08953538522663743</v>
+      </c>
+      <c r="I56" t="n">
         <v>0.3393165135782333</v>
       </c>
-      <c r="F56" t="n">
-        <v>0.08851617587476523</v>
-      </c>
-      <c r="G56" t="n">
-        <v>0.6014116058643056</v>
-      </c>
-      <c r="H56" t="n">
-        <v>0.08666488603711876</v>
-      </c>
-      <c r="I56" t="n">
-        <v>0.6014116058643056</v>
-      </c>
       <c r="J56" t="n">
-        <v>0.08816840369615396</v>
+        <v>0.08787047251319219</v>
       </c>
       <c r="K56" t="n">
         <v>0.3393165135782333</v>
@@ -2541,19 +2541,19 @@
         <v>0.08</v>
       </c>
       <c r="E57" t="n">
+        <v>0.6014116058643056</v>
+      </c>
+      <c r="F57" t="n">
+        <v>0</v>
+      </c>
+      <c r="G57" t="n">
+        <v>0.6014116058643056</v>
+      </c>
+      <c r="H57" t="n">
+        <v>0</v>
+      </c>
+      <c r="I57" t="n">
         <v>0.1323240299819102</v>
-      </c>
-      <c r="F57" t="n">
-        <v>0</v>
-      </c>
-      <c r="G57" t="n">
-        <v>0.6014116058643056</v>
-      </c>
-      <c r="H57" t="n">
-        <v>0</v>
-      </c>
-      <c r="I57" t="n">
-        <v>0.6014116058643056</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -2578,19 +2578,19 @@
         <v>0.08</v>
       </c>
       <c r="E58" t="n">
+        <v>0.6014116058643056</v>
+      </c>
+      <c r="F58" t="n">
+        <v>0</v>
+      </c>
+      <c r="G58" t="n">
+        <v>0.6014116058643056</v>
+      </c>
+      <c r="H58" t="n">
+        <v>0</v>
+      </c>
+      <c r="I58" t="n">
         <v>0.2154936369329378</v>
-      </c>
-      <c r="F58" t="n">
-        <v>0</v>
-      </c>
-      <c r="G58" t="n">
-        <v>0.6014116058643056</v>
-      </c>
-      <c r="H58" t="n">
-        <v>0</v>
-      </c>
-      <c r="I58" t="n">
-        <v>0.6014116058643056</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -2615,19 +2615,19 @@
         <v>0.08</v>
       </c>
       <c r="E59" t="n">
+        <v>0.6014116058643056</v>
+      </c>
+      <c r="F59" t="n">
+        <v>0</v>
+      </c>
+      <c r="G59" t="n">
+        <v>0.6014116058643056</v>
+      </c>
+      <c r="H59" t="n">
+        <v>0</v>
+      </c>
+      <c r="I59" t="n">
         <v>0.2711964643509661</v>
-      </c>
-      <c r="F59" t="n">
-        <v>0</v>
-      </c>
-      <c r="G59" t="n">
-        <v>0.6014116058643056</v>
-      </c>
-      <c r="H59" t="n">
-        <v>0</v>
-      </c>
-      <c r="I59" t="n">
-        <v>0.6014116058643056</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -2652,19 +2652,19 @@
         <v>0.08</v>
       </c>
       <c r="E60" t="n">
+        <v>0.6014116058643056</v>
+      </c>
+      <c r="F60" t="n">
+        <v>0</v>
+      </c>
+      <c r="G60" t="n">
+        <v>0.6014116058643056</v>
+      </c>
+      <c r="H60" t="n">
+        <v>0</v>
+      </c>
+      <c r="I60" t="n">
         <v>0.3104699533606</v>
-      </c>
-      <c r="F60" t="n">
-        <v>0</v>
-      </c>
-      <c r="G60" t="n">
-        <v>0.6014116058643056</v>
-      </c>
-      <c r="H60" t="n">
-        <v>0</v>
-      </c>
-      <c r="I60" t="n">
-        <v>0.6014116058643056</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -2689,19 +2689,19 @@
         <v>0.08</v>
       </c>
       <c r="E61" t="n">
+        <v>0.6014116058643056</v>
+      </c>
+      <c r="F61" t="n">
+        <v>0</v>
+      </c>
+      <c r="G61" t="n">
+        <v>0.6014116058643056</v>
+      </c>
+      <c r="H61" t="n">
+        <v>0</v>
+      </c>
+      <c r="I61" t="n">
         <v>0.3393165135782333</v>
-      </c>
-      <c r="F61" t="n">
-        <v>0</v>
-      </c>
-      <c r="G61" t="n">
-        <v>0.6014116058643056</v>
-      </c>
-      <c r="H61" t="n">
-        <v>0</v>
-      </c>
-      <c r="I61" t="n">
-        <v>0.6014116058643056</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -2752,7 +2752,7 @@
         <v>47849</v>
       </c>
       <c r="B63" t="n">
-        <v>0.03876591992944924</v>
+        <v>0.02704542472809291</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -2766,19 +2766,19 @@
         <v>0.6014116058643056</v>
       </c>
       <c r="F63" t="n">
-        <v>0.04097449930278309</v>
+        <v>0.02733684885579852</v>
       </c>
       <c r="G63" t="n">
         <v>0.6014116058643056</v>
       </c>
       <c r="H63" t="n">
-        <v>0.04186729551757756</v>
+        <v>0.0268273047537855</v>
       </c>
       <c r="I63" t="n">
         <v>0.6014116058643056</v>
       </c>
       <c r="J63" t="n">
-        <v>0.03708146432864604</v>
+        <v>0.02890614288379727</v>
       </c>
       <c r="K63" t="n">
         <v>0.6014116058643056</v>
@@ -2789,7 +2789,7 @@
         <v>49675</v>
       </c>
       <c r="B64" t="n">
-        <v>0.03876591992944924</v>
+        <v>0.02825293202083202</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -2803,19 +2803,19 @@
         <v>0.6014116058643056</v>
       </c>
       <c r="F64" t="n">
-        <v>0.04097449930278309</v>
+        <v>0.02850230997910832</v>
       </c>
       <c r="G64" t="n">
         <v>0.6014116058643056</v>
       </c>
       <c r="H64" t="n">
-        <v>0.04186729551757756</v>
+        <v>0.02960390291548299</v>
       </c>
       <c r="I64" t="n">
         <v>0.6014116058643056</v>
       </c>
       <c r="J64" t="n">
-        <v>0.03708146432864604</v>
+        <v>0.03168912069755178</v>
       </c>
       <c r="K64" t="n">
         <v>0.6014116058643056</v>
@@ -2826,7 +2826,7 @@
         <v>51502</v>
       </c>
       <c r="B65" t="n">
-        <v>0.04582774240370474</v>
+        <v>0.02879914740894986</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -2840,19 +2840,19 @@
         <v>0.6014116058643056</v>
       </c>
       <c r="F65" t="n">
-        <v>0.04818170170618283</v>
+        <v>0.03358624213250979</v>
       </c>
       <c r="G65" t="n">
         <v>0.6014116058643056</v>
       </c>
       <c r="H65" t="n">
-        <v>0.04951794975111175</v>
+        <v>0.03947728081126527</v>
       </c>
       <c r="I65" t="n">
         <v>0.6014116058643056</v>
       </c>
       <c r="J65" t="n">
-        <v>0.04468502613570808</v>
+        <v>0.03948165200371508</v>
       </c>
       <c r="K65" t="n">
         <v>0.6014116058643056</v>
@@ -2863,7 +2863,7 @@
         <v>53328</v>
       </c>
       <c r="B66" t="n">
-        <v>0.04154502749107446</v>
+        <v>0.02656257282647543</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -2877,19 +2877,19 @@
         <v>0.6014116058643056</v>
       </c>
       <c r="F66" t="n">
-        <v>0.04201971159460979</v>
+        <v>0.02649150038097193</v>
       </c>
       <c r="G66" t="n">
         <v>0.6014116058643056</v>
       </c>
       <c r="H66" t="n">
-        <v>0.04400166300111176</v>
+        <v>0.03021867751820156</v>
       </c>
       <c r="I66" t="n">
         <v>0.6014116058643056</v>
       </c>
       <c r="J66" t="n">
-        <v>0.03880793799466955</v>
+        <v>0.03191990897007307</v>
       </c>
       <c r="K66" t="n">
         <v>0.6014116058643056</v>
@@ -3096,7 +3096,7 @@
         <v>0.08</v>
       </c>
       <c r="E72" t="n">
-        <v>0.03682040983458015</v>
+        <v>0.6014116058643056</v>
       </c>
       <c r="F72" t="n">
         <v>0</v>
@@ -3114,7 +3114,7 @@
         <v>0</v>
       </c>
       <c r="K72" t="n">
-        <v>0.03682040983458015</v>
+        <v>0.6014116058643056</v>
       </c>
     </row>
     <row r="73">
@@ -3133,7 +3133,7 @@
         <v>0.08</v>
       </c>
       <c r="E73" t="n">
-        <v>0.06568130249835975</v>
+        <v>0.6014116058643056</v>
       </c>
       <c r="F73" t="n">
         <v>0</v>
@@ -3151,7 +3151,7 @@
         <v>0</v>
       </c>
       <c r="K73" t="n">
-        <v>0.06568130249835975</v>
+        <v>0.6014116058643056</v>
       </c>
     </row>
     <row r="74">
@@ -3170,7 +3170,7 @@
         <v>0.08</v>
       </c>
       <c r="E74" t="n">
-        <v>0.08919625628063554</v>
+        <v>0.6014116058643056</v>
       </c>
       <c r="F74" t="n">
         <v>0</v>
@@ -3188,7 +3188,7 @@
         <v>0</v>
       </c>
       <c r="K74" t="n">
-        <v>0.08919625628063554</v>
+        <v>0.6014116058643056</v>
       </c>
     </row>
     <row r="75">
@@ -3207,7 +3207,7 @@
         <v>0.08</v>
       </c>
       <c r="E75" t="n">
-        <v>0.1089050369639545</v>
+        <v>0.6014116058643056</v>
       </c>
       <c r="F75" t="n">
         <v>0</v>
@@ -3225,7 +3225,7 @@
         <v>0</v>
       </c>
       <c r="K75" t="n">
-        <v>0.1089050369639545</v>
+        <v>0.6014116058643056</v>
       </c>
     </row>
     <row r="76">
@@ -3244,7 +3244,7 @@
         <v>0.08</v>
       </c>
       <c r="E76" t="n">
-        <v>0.1257467230135668</v>
+        <v>0.6014116058643056</v>
       </c>
       <c r="F76" t="n">
         <v>0</v>
@@ -3262,7 +3262,7 @@
         <v>0</v>
       </c>
       <c r="K76" t="n">
-        <v>0.1257467230135668</v>
+        <v>0.6014116058643056</v>
       </c>
     </row>
     <row r="77">
@@ -3270,7 +3270,7 @@
         <v>46023</v>
       </c>
       <c r="B77" t="n">
-        <v>0</v>
+        <v>0.003097719647034781</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -3281,25 +3281,25 @@
         <v>0.08</v>
       </c>
       <c r="E77" t="n">
-        <v>0.03682040983458015</v>
+        <v>0.6014116058643056</v>
       </c>
       <c r="F77" t="n">
-        <v>0.0009107054164868193</v>
+        <v>0</v>
       </c>
       <c r="G77" t="n">
         <v>0.6014116058643056</v>
       </c>
       <c r="H77" t="n">
-        <v>0</v>
+        <v>0.009722739192653906</v>
       </c>
       <c r="I77" t="n">
         <v>0.6014116058643056</v>
       </c>
       <c r="J77" t="n">
-        <v>0.002024404848985258</v>
+        <v>0</v>
       </c>
       <c r="K77" t="n">
-        <v>0.03682040983458015</v>
+        <v>0.6014116058643056</v>
       </c>
     </row>
     <row r="78">
@@ -3307,7 +3307,7 @@
         <v>47849</v>
       </c>
       <c r="B78" t="n">
-        <v>0</v>
+        <v>0.003097719647034781</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -3318,25 +3318,25 @@
         <v>0.08</v>
       </c>
       <c r="E78" t="n">
-        <v>0.06568130249835975</v>
+        <v>0.6014116058643056</v>
       </c>
       <c r="F78" t="n">
-        <v>0.0009107054164868193</v>
+        <v>0</v>
       </c>
       <c r="G78" t="n">
         <v>0.6014116058643056</v>
       </c>
       <c r="H78" t="n">
-        <v>0</v>
+        <v>0.009722739192653906</v>
       </c>
       <c r="I78" t="n">
         <v>0.6014116058643056</v>
       </c>
       <c r="J78" t="n">
-        <v>0.002024404848985258</v>
+        <v>0</v>
       </c>
       <c r="K78" t="n">
-        <v>0.06568130249835975</v>
+        <v>0.6014116058643056</v>
       </c>
     </row>
     <row r="79">
@@ -3344,7 +3344,7 @@
         <v>49675</v>
       </c>
       <c r="B79" t="n">
-        <v>0</v>
+        <v>0.003097719647034781</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -3355,25 +3355,25 @@
         <v>0.08</v>
       </c>
       <c r="E79" t="n">
-        <v>0.08919625628063554</v>
+        <v>0.6014116058643056</v>
       </c>
       <c r="F79" t="n">
-        <v>0.0009107054164868193</v>
+        <v>0</v>
       </c>
       <c r="G79" t="n">
         <v>0.6014116058643056</v>
       </c>
       <c r="H79" t="n">
-        <v>0</v>
+        <v>0.009722739192653906</v>
       </c>
       <c r="I79" t="n">
         <v>0.6014116058643056</v>
       </c>
       <c r="J79" t="n">
-        <v>0.002024404848985258</v>
+        <v>0</v>
       </c>
       <c r="K79" t="n">
-        <v>0.08919625628063554</v>
+        <v>0.6014116058643056</v>
       </c>
     </row>
     <row r="80">
@@ -3392,7 +3392,7 @@
         <v>0.08</v>
       </c>
       <c r="E80" t="n">
-        <v>0.1089050369639545</v>
+        <v>0.6014116058643056</v>
       </c>
       <c r="F80" t="n">
         <v>0</v>
@@ -3410,7 +3410,7 @@
         <v>0</v>
       </c>
       <c r="K80" t="n">
-        <v>0.1089050369639545</v>
+        <v>0.6014116058643056</v>
       </c>
     </row>
     <row r="81">
@@ -3429,7 +3429,7 @@
         <v>0.08</v>
       </c>
       <c r="E81" t="n">
-        <v>0.1257467230135668</v>
+        <v>0.6014116058643056</v>
       </c>
       <c r="F81" t="n">
         <v>0</v>
@@ -3447,7 +3447,7 @@
         <v>0</v>
       </c>
       <c r="K81" t="n">
-        <v>0.1257467230135668</v>
+        <v>0.6014116058643056</v>
       </c>
     </row>
     <row r="82">
@@ -3464,19 +3464,19 @@
       </c>
       <c r="D82" t="inlineStr"/>
       <c r="E82" t="n">
+        <v>1</v>
+      </c>
+      <c r="F82" t="n">
+        <v>0</v>
+      </c>
+      <c r="G82" t="n">
+        <v>1</v>
+      </c>
+      <c r="H82" t="n">
+        <v>0</v>
+      </c>
+      <c r="I82" t="n">
         <v>0.2712070570783821</v>
-      </c>
-      <c r="F82" t="n">
-        <v>0</v>
-      </c>
-      <c r="G82" t="n">
-        <v>1</v>
-      </c>
-      <c r="H82" t="n">
-        <v>0</v>
-      </c>
-      <c r="I82" t="n">
-        <v>1</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -3499,19 +3499,19 @@
       </c>
       <c r="D83" t="inlineStr"/>
       <c r="E83" t="n">
+        <v>1</v>
+      </c>
+      <c r="F83" t="n">
+        <v>0</v>
+      </c>
+      <c r="G83" t="n">
+        <v>1</v>
+      </c>
+      <c r="H83" t="n">
+        <v>0</v>
+      </c>
+      <c r="I83" t="n">
         <v>0.4370978189737727</v>
-      </c>
-      <c r="F83" t="n">
-        <v>0</v>
-      </c>
-      <c r="G83" t="n">
-        <v>1</v>
-      </c>
-      <c r="H83" t="n">
-        <v>0</v>
-      </c>
-      <c r="I83" t="n">
-        <v>1</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -3534,19 +3534,19 @@
       </c>
       <c r="D84" t="inlineStr"/>
       <c r="E84" t="n">
+        <v>1</v>
+      </c>
+      <c r="F84" t="n">
+        <v>0</v>
+      </c>
+      <c r="G84" t="n">
+        <v>1</v>
+      </c>
+      <c r="H84" t="n">
+        <v>0</v>
+      </c>
+      <c r="I84" t="n">
         <v>0.5456964388783678</v>
-      </c>
-      <c r="F84" t="n">
-        <v>0</v>
-      </c>
-      <c r="G84" t="n">
-        <v>1</v>
-      </c>
-      <c r="H84" t="n">
-        <v>0</v>
-      </c>
-      <c r="I84" t="n">
-        <v>1</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -3569,19 +3569,19 @@
       </c>
       <c r="D85" t="inlineStr"/>
       <c r="E85" t="n">
+        <v>1</v>
+      </c>
+      <c r="F85" t="n">
+        <v>0</v>
+      </c>
+      <c r="G85" t="n">
+        <v>1</v>
+      </c>
+      <c r="H85" t="n">
+        <v>0</v>
+      </c>
+      <c r="I85" t="n">
         <v>0.6207578627767205</v>
-      </c>
-      <c r="F85" t="n">
-        <v>0</v>
-      </c>
-      <c r="G85" t="n">
-        <v>1</v>
-      </c>
-      <c r="H85" t="n">
-        <v>0</v>
-      </c>
-      <c r="I85" t="n">
-        <v>1</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -3604,19 +3604,19 @@
       </c>
       <c r="D86" t="inlineStr"/>
       <c r="E86" t="n">
+        <v>1</v>
+      </c>
+      <c r="F86" t="n">
+        <v>0</v>
+      </c>
+      <c r="G86" t="n">
+        <v>1</v>
+      </c>
+      <c r="H86" t="n">
+        <v>0</v>
+      </c>
+      <c r="I86" t="n">
         <v>0.6749874416447547</v>
-      </c>
-      <c r="F86" t="n">
-        <v>0</v>
-      </c>
-      <c r="G86" t="n">
-        <v>1</v>
-      </c>
-      <c r="H86" t="n">
-        <v>0</v>
-      </c>
-      <c r="I86" t="n">
-        <v>1</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -3639,19 +3639,19 @@
       </c>
       <c r="D87" t="inlineStr"/>
       <c r="E87" t="n">
+        <v>1</v>
+      </c>
+      <c r="F87" t="n">
+        <v>0</v>
+      </c>
+      <c r="G87" t="n">
+        <v>1</v>
+      </c>
+      <c r="H87" t="n">
+        <v>0</v>
+      </c>
+      <c r="I87" t="n">
         <v>0.2712070570783821</v>
-      </c>
-      <c r="F87" t="n">
-        <v>0</v>
-      </c>
-      <c r="G87" t="n">
-        <v>1</v>
-      </c>
-      <c r="H87" t="n">
-        <v>0</v>
-      </c>
-      <c r="I87" t="n">
-        <v>1</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -3674,19 +3674,19 @@
       </c>
       <c r="D88" t="inlineStr"/>
       <c r="E88" t="n">
+        <v>1</v>
+      </c>
+      <c r="F88" t="n">
+        <v>0</v>
+      </c>
+      <c r="G88" t="n">
+        <v>1</v>
+      </c>
+      <c r="H88" t="n">
+        <v>0</v>
+      </c>
+      <c r="I88" t="n">
         <v>0.4370978189737727</v>
-      </c>
-      <c r="F88" t="n">
-        <v>0</v>
-      </c>
-      <c r="G88" t="n">
-        <v>1</v>
-      </c>
-      <c r="H88" t="n">
-        <v>0</v>
-      </c>
-      <c r="I88" t="n">
-        <v>1</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -3709,19 +3709,19 @@
       </c>
       <c r="D89" t="inlineStr"/>
       <c r="E89" t="n">
+        <v>1</v>
+      </c>
+      <c r="F89" t="n">
+        <v>0</v>
+      </c>
+      <c r="G89" t="n">
+        <v>1</v>
+      </c>
+      <c r="H89" t="n">
+        <v>0</v>
+      </c>
+      <c r="I89" t="n">
         <v>0.5456964388783678</v>
-      </c>
-      <c r="F89" t="n">
-        <v>0</v>
-      </c>
-      <c r="G89" t="n">
-        <v>1</v>
-      </c>
-      <c r="H89" t="n">
-        <v>0</v>
-      </c>
-      <c r="I89" t="n">
-        <v>1</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -3744,19 +3744,19 @@
       </c>
       <c r="D90" t="inlineStr"/>
       <c r="E90" t="n">
+        <v>1</v>
+      </c>
+      <c r="F90" t="n">
+        <v>0</v>
+      </c>
+      <c r="G90" t="n">
+        <v>1</v>
+      </c>
+      <c r="H90" t="n">
+        <v>0</v>
+      </c>
+      <c r="I90" t="n">
         <v>0.6207578627767205</v>
-      </c>
-      <c r="F90" t="n">
-        <v>0</v>
-      </c>
-      <c r="G90" t="n">
-        <v>1</v>
-      </c>
-      <c r="H90" t="n">
-        <v>0</v>
-      </c>
-      <c r="I90" t="n">
-        <v>1</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -3779,19 +3779,19 @@
       </c>
       <c r="D91" t="inlineStr"/>
       <c r="E91" t="n">
+        <v>1</v>
+      </c>
+      <c r="F91" t="n">
+        <v>0</v>
+      </c>
+      <c r="G91" t="n">
+        <v>1</v>
+      </c>
+      <c r="H91" t="n">
+        <v>0</v>
+      </c>
+      <c r="I91" t="n">
         <v>0.6749874416447547</v>
-      </c>
-      <c r="F91" t="n">
-        <v>0</v>
-      </c>
-      <c r="G91" t="n">
-        <v>1</v>
-      </c>
-      <c r="H91" t="n">
-        <v>0</v>
-      </c>
-      <c r="I91" t="n">
-        <v>1</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -3814,19 +3814,19 @@
       </c>
       <c r="D92" t="inlineStr"/>
       <c r="E92" t="n">
+        <v>1</v>
+      </c>
+      <c r="F92" t="n">
+        <v>0</v>
+      </c>
+      <c r="G92" t="n">
+        <v>1</v>
+      </c>
+      <c r="H92" t="n">
+        <v>0</v>
+      </c>
+      <c r="I92" t="n">
         <v>0.2712070570783821</v>
-      </c>
-      <c r="F92" t="n">
-        <v>0</v>
-      </c>
-      <c r="G92" t="n">
-        <v>1</v>
-      </c>
-      <c r="H92" t="n">
-        <v>0</v>
-      </c>
-      <c r="I92" t="n">
-        <v>1</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -3849,19 +3849,19 @@
       </c>
       <c r="D93" t="inlineStr"/>
       <c r="E93" t="n">
+        <v>1</v>
+      </c>
+      <c r="F93" t="n">
+        <v>0</v>
+      </c>
+      <c r="G93" t="n">
+        <v>1</v>
+      </c>
+      <c r="H93" t="n">
+        <v>0</v>
+      </c>
+      <c r="I93" t="n">
         <v>0.4370978189737727</v>
-      </c>
-      <c r="F93" t="n">
-        <v>0</v>
-      </c>
-      <c r="G93" t="n">
-        <v>1</v>
-      </c>
-      <c r="H93" t="n">
-        <v>0</v>
-      </c>
-      <c r="I93" t="n">
-        <v>1</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -3884,19 +3884,19 @@
       </c>
       <c r="D94" t="inlineStr"/>
       <c r="E94" t="n">
+        <v>1</v>
+      </c>
+      <c r="F94" t="n">
+        <v>0</v>
+      </c>
+      <c r="G94" t="n">
+        <v>1</v>
+      </c>
+      <c r="H94" t="n">
+        <v>0</v>
+      </c>
+      <c r="I94" t="n">
         <v>0.5456964388783678</v>
-      </c>
-      <c r="F94" t="n">
-        <v>0</v>
-      </c>
-      <c r="G94" t="n">
-        <v>1</v>
-      </c>
-      <c r="H94" t="n">
-        <v>0</v>
-      </c>
-      <c r="I94" t="n">
-        <v>1</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -3919,19 +3919,19 @@
       </c>
       <c r="D95" t="inlineStr"/>
       <c r="E95" t="n">
+        <v>1</v>
+      </c>
+      <c r="F95" t="n">
+        <v>0</v>
+      </c>
+      <c r="G95" t="n">
+        <v>1</v>
+      </c>
+      <c r="H95" t="n">
+        <v>0</v>
+      </c>
+      <c r="I95" t="n">
         <v>0.6207578627767205</v>
-      </c>
-      <c r="F95" t="n">
-        <v>0</v>
-      </c>
-      <c r="G95" t="n">
-        <v>1</v>
-      </c>
-      <c r="H95" t="n">
-        <v>0</v>
-      </c>
-      <c r="I95" t="n">
-        <v>1</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -3954,19 +3954,19 @@
       </c>
       <c r="D96" t="inlineStr"/>
       <c r="E96" t="n">
+        <v>1</v>
+      </c>
+      <c r="F96" t="n">
+        <v>0</v>
+      </c>
+      <c r="G96" t="n">
+        <v>1</v>
+      </c>
+      <c r="H96" t="n">
+        <v>0</v>
+      </c>
+      <c r="I96" t="n">
         <v>0.6749874416447547</v>
-      </c>
-      <c r="F96" t="n">
-        <v>0</v>
-      </c>
-      <c r="G96" t="n">
-        <v>1</v>
-      </c>
-      <c r="H96" t="n">
-        <v>0</v>
-      </c>
-      <c r="I96" t="n">
-        <v>1</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
